--- a/data/floor_plans_raw.xlsx
+++ b/data/floor_plans_raw.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\building_impact_model\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C566238-F53F-4B28-82E9-7F3BE666CCDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{801BA130-BA89-4519-B388-DDEDD38B2183}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28770" yWindow="30" windowWidth="28770" windowHeight="15450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="floor_plans" sheetId="9" r:id="rId1"/>
@@ -3926,7 +3926,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2028" uniqueCount="670">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1692" uniqueCount="594">
   <si>
     <t>type</t>
   </si>
@@ -4486,130 +4486,25 @@
     <t>51750HZ</t>
   </si>
   <si>
-    <t>222</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
     <t>5141MM</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>600</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>105</t>
-  </si>
-  <si>
-    <t>212</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>0.5</t>
   </si>
   <si>
     <t>51020MM</t>
   </si>
   <si>
-    <t>950</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>136</t>
-  </si>
-  <si>
-    <t>272</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
     <t>11722HZ</t>
-  </si>
-  <si>
-    <t>850</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>126</t>
-  </si>
-  <si>
-    <t>277</t>
   </si>
   <si>
     <t>5153MM</t>
   </si>
   <si>
-    <t>800</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>120</t>
-  </si>
-  <si>
-    <t>244</t>
-  </si>
-  <si>
     <t>11724HZ</t>
-  </si>
-  <si>
-    <t>900</t>
-  </si>
-  <si>
-    <t>150</t>
-  </si>
-  <si>
-    <t>363</t>
-  </si>
-  <si>
-    <t>35</t>
   </si>
   <si>
     <t>11725HZ</t>
   </si>
   <si>
-    <t>323</t>
-  </si>
-  <si>
     <t>11723HZ</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>330</t>
   </si>
   <si>
     <t>5154MM</t>
@@ -4621,124 +4516,25 @@
     <t>51181MM</t>
   </si>
   <si>
-    <t>1233</t>
-  </si>
-  <si>
-    <t>1016</t>
-  </si>
-  <si>
-    <t>217</t>
-  </si>
-  <si>
-    <t>246</t>
-  </si>
-  <si>
-    <t>43</t>
-  </si>
-  <si>
     <t>51011MM</t>
-  </si>
-  <si>
-    <t>1100</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>142</t>
-  </si>
-  <si>
-    <t>348</t>
   </si>
   <si>
     <t>11717HZ</t>
   </si>
   <si>
-    <t>1200</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>160</t>
-  </si>
-  <si>
-    <t>417</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
     <t>11738HZ</t>
-  </si>
-  <si>
-    <t>8.5</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>168</t>
-  </si>
-  <si>
-    <t>442</t>
-  </si>
-  <si>
-    <t>54</t>
   </si>
   <si>
     <t>51115MM</t>
   </si>
   <si>
-    <t>186</t>
-  </si>
-  <si>
-    <t>409</t>
-  </si>
-  <si>
-    <t>60</t>
-  </si>
-  <si>
     <t>51149MM</t>
-  </si>
-  <si>
-    <t>1216</t>
-  </si>
-  <si>
-    <t>194</t>
-  </si>
-  <si>
-    <t>441</t>
-  </si>
-  <si>
-    <t>62</t>
   </si>
   <si>
     <t>51790HZ</t>
   </si>
   <si>
-    <t>1232</t>
-  </si>
-  <si>
-    <t>200</t>
-  </si>
-  <si>
-    <t>420</t>
-  </si>
-  <si>
     <t>5167MM</t>
-  </si>
-  <si>
-    <t>1250</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>460</t>
-  </si>
-  <si>
-    <t>64</t>
   </si>
   <si>
     <t>11739HZ</t>
@@ -4747,13 +4543,7 @@
     <t>5102MM</t>
   </si>
   <si>
-    <t>1251</t>
-  </si>
-  <si>
     <t>11740HZ</t>
-  </si>
-  <si>
-    <t>1300</t>
   </si>
   <si>
     <t>11757HZ</t>
@@ -4762,37 +4552,19 @@
     <t>51129MM</t>
   </si>
   <si>
-    <t>1310</t>
-  </si>
-  <si>
     <t>11718HZ</t>
-  </si>
-  <si>
-    <t>1350</t>
   </si>
   <si>
     <t>51113MM</t>
   </si>
   <si>
-    <t>1354</t>
-  </si>
-  <si>
     <t>11741HZ</t>
-  </si>
-  <si>
-    <t>1375</t>
   </si>
   <si>
     <t>51731HZ</t>
   </si>
   <si>
-    <t>1381</t>
-  </si>
-  <si>
     <t>51811HZ</t>
-  </si>
-  <si>
-    <t>1398</t>
   </si>
   <si>
     <t>5104MM</t>
@@ -5995,7 +5767,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -6025,6 +5797,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -7723,7 +7498,7 @@
     <col min="23" max="24" width="8.875" style="1" customWidth="1"/>
     <col min="25" max="25" width="5.75" style="1" customWidth="1"/>
     <col min="26" max="26" width="6.125" style="1" customWidth="1"/>
-    <col min="27" max="27" width="5.125" style="1" hidden="1" customWidth="1"/>
+    <col min="27" max="27" width="5.125" style="1" customWidth="1"/>
     <col min="28" max="28" width="6.5" style="1" customWidth="1"/>
     <col min="29" max="29" width="8.875" style="1"/>
     <col min="30" max="30" width="16.25" style="1" customWidth="1"/>
@@ -7831,7 +7606,7 @@
     </row>
     <row r="2" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>559</v>
+        <v>483</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>32</v>
@@ -7926,7 +7701,7 @@
     </row>
     <row r="3" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>291</v>
+        <v>215</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>32</v>
@@ -7935,7 +7710,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>290</v>
+        <v>214</v>
       </c>
       <c r="E3" s="5">
         <v>1</v>
@@ -8023,7 +7798,7 @@
     </row>
     <row r="4" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>313</v>
+        <v>237</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>32</v>
@@ -8118,7 +7893,7 @@
     </row>
     <row r="5" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>494</v>
+        <v>418</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>32</v>
@@ -8217,7 +7992,7 @@
     </row>
     <row r="6" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>497</v>
+        <v>421</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>32</v>
@@ -8316,7 +8091,7 @@
     </row>
     <row r="7" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>563</v>
+        <v>487</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>32</v>
@@ -8411,7 +8186,7 @@
     </row>
     <row r="8" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>571</v>
+        <v>495</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>32</v>
@@ -8506,7 +8281,7 @@
     </row>
     <row r="9" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>327</v>
+        <v>251</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>32</v>
@@ -8601,7 +8376,7 @@
     </row>
     <row r="10" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>589</v>
+        <v>513</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>32</v>
@@ -8696,7 +8471,7 @@
     </row>
     <row r="11" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>415</v>
+        <v>339</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>32</v>
@@ -8791,7 +8566,7 @@
     </row>
     <row r="12" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>421</v>
+        <v>345</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>32</v>
@@ -8886,7 +8661,7 @@
     </row>
     <row r="13" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>526</v>
+        <v>450</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>32</v>
@@ -8981,7 +8756,7 @@
     </row>
     <row r="14" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>430</v>
+        <v>354</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>32</v>
@@ -9076,7 +8851,7 @@
     </row>
     <row r="15" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>533</v>
+        <v>457</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>32</v>
@@ -9171,7 +8946,7 @@
     </row>
     <row r="16" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>506</v>
+        <v>430</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>32</v>
@@ -9270,7 +9045,7 @@
     </row>
     <row r="17" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>572</v>
+        <v>496</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>32</v>
@@ -9365,7 +9140,7 @@
     </row>
     <row r="18" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>328</v>
+        <v>252</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>32</v>
@@ -9460,7 +9235,7 @@
     </row>
     <row r="19" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>241</v>
+        <v>197</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>32</v>
@@ -9468,74 +9243,74 @@
       <c r="C19" s="1">
         <v>1</v>
       </c>
-      <c r="D19" s="1" t="s">
-        <v>242</v>
+      <c r="D19" s="11">
+        <v>1200</v>
       </c>
       <c r="E19" s="5">
         <v>1</v>
       </c>
-      <c r="F19" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="J19" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="K19" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="L19" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="M19" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="N19" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="O19" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="P19" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="Q19" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="R19" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="S19" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="T19" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="U19" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="W19" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="X19" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="Y19" s="1" t="s">
-        <v>203</v>
+      <c r="F19" s="11">
+        <v>1200</v>
+      </c>
+      <c r="G19" s="11">
+        <v>0</v>
+      </c>
+      <c r="H19" s="11">
+        <v>9</v>
+      </c>
+      <c r="I19" s="11">
+        <v>0</v>
+      </c>
+      <c r="J19" s="11">
+        <v>3</v>
+      </c>
+      <c r="K19" s="11">
+        <v>0</v>
+      </c>
+      <c r="L19" s="11">
+        <v>2</v>
+      </c>
+      <c r="M19" s="11">
+        <v>0</v>
+      </c>
+      <c r="N19" s="11">
+        <v>7</v>
+      </c>
+      <c r="O19" s="11">
+        <v>0</v>
+      </c>
+      <c r="P19" s="11">
+        <v>14</v>
+      </c>
+      <c r="Q19" s="11">
+        <v>4</v>
+      </c>
+      <c r="R19" s="11">
+        <v>0</v>
+      </c>
+      <c r="S19" s="11">
+        <v>0</v>
+      </c>
+      <c r="T19" s="11">
+        <v>160</v>
+      </c>
+      <c r="U19" s="11">
+        <v>417</v>
+      </c>
+      <c r="W19" s="11">
+        <v>0</v>
+      </c>
+      <c r="X19" s="11">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="11">
+        <v>9</v>
       </c>
       <c r="Z19" s="1">
         <v>0.58299999999999996</v>
       </c>
-      <c r="AA19" s="1" t="s">
-        <v>246</v>
+      <c r="AA19" s="11">
+        <v>40</v>
       </c>
       <c r="AB19" s="1">
         <v>20.2</v>
@@ -9556,7 +9331,7 @@
     </row>
     <row r="20" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>279</v>
+        <v>208</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>32</v>
@@ -9564,8 +9339,8 @@
       <c r="C20" s="1">
         <v>1</v>
       </c>
-      <c r="D20" s="1" t="s">
-        <v>280</v>
+      <c r="D20" s="11">
+        <v>1350</v>
       </c>
       <c r="E20" s="5">
         <v>1</v>
@@ -9653,7 +9428,7 @@
     </row>
     <row r="21" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>317</v>
+        <v>241</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>32</v>
@@ -9748,7 +9523,7 @@
     </row>
     <row r="22" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>507</v>
+        <v>431</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>32</v>
@@ -9847,7 +9622,7 @@
     </row>
     <row r="23" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>207</v>
+        <v>188</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>32</v>
@@ -9855,74 +9630,74 @@
       <c r="C23" s="1">
         <v>1</v>
       </c>
-      <c r="D23" s="1" t="s">
-        <v>208</v>
+      <c r="D23" s="11">
+        <v>850</v>
       </c>
       <c r="E23" s="5">
         <v>1</v>
       </c>
-      <c r="F23" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="J23" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="L23" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="M23" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="N23" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="O23" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="P23" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="Q23" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="R23" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="S23" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="T23" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="U23" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="W23" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="X23" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="Y23" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="Z23" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="AA23" s="1" t="s">
-        <v>187</v>
+      <c r="F23" s="11">
+        <v>850</v>
+      </c>
+      <c r="G23" s="11">
+        <v>0</v>
+      </c>
+      <c r="H23" s="11">
+        <v>8</v>
+      </c>
+      <c r="I23" s="11">
+        <v>0</v>
+      </c>
+      <c r="J23" s="11">
+        <v>2</v>
+      </c>
+      <c r="K23" s="11">
+        <v>0</v>
+      </c>
+      <c r="L23" s="11">
+        <v>1</v>
+      </c>
+      <c r="M23" s="11">
+        <v>0</v>
+      </c>
+      <c r="N23" s="11">
+        <v>8</v>
+      </c>
+      <c r="O23" s="11">
+        <v>0</v>
+      </c>
+      <c r="P23" s="11">
+        <v>10</v>
+      </c>
+      <c r="Q23" s="11">
+        <v>2</v>
+      </c>
+      <c r="R23" s="11">
+        <v>0</v>
+      </c>
+      <c r="S23" s="11">
+        <v>0</v>
+      </c>
+      <c r="T23" s="11">
+        <v>126</v>
+      </c>
+      <c r="U23" s="11">
+        <v>277</v>
+      </c>
+      <c r="W23" s="11">
+        <v>0</v>
+      </c>
+      <c r="X23" s="11">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="11">
+        <v>8</v>
+      </c>
+      <c r="Z23" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="AA23" s="11">
+        <v>32</v>
       </c>
       <c r="AB23" s="1">
         <v>17.5</v>
@@ -9943,7 +9718,7 @@
     </row>
     <row r="24" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>225</v>
+        <v>192</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>32</v>
@@ -9951,74 +9726,74 @@
       <c r="C24" s="1">
         <v>1</v>
       </c>
-      <c r="D24" s="1" t="s">
-        <v>219</v>
+      <c r="D24" s="11">
+        <v>900</v>
       </c>
       <c r="E24" s="5">
         <v>1</v>
       </c>
-      <c r="F24" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="J24" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="K24" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="L24" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="M24" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="N24" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="O24" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="P24" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="Q24" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="R24" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="S24" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="T24" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="U24" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="W24" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="X24" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="Y24" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="Z24" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="AA24" s="1" t="s">
-        <v>198</v>
+      <c r="F24" s="11">
+        <v>900</v>
+      </c>
+      <c r="G24" s="11">
+        <v>0</v>
+      </c>
+      <c r="H24" s="11">
+        <v>8</v>
+      </c>
+      <c r="I24" s="11">
+        <v>0</v>
+      </c>
+      <c r="J24" s="11">
+        <v>2</v>
+      </c>
+      <c r="K24" s="11">
+        <v>0</v>
+      </c>
+      <c r="L24" s="11">
+        <v>1</v>
+      </c>
+      <c r="M24" s="11">
+        <v>0</v>
+      </c>
+      <c r="N24" s="11">
+        <v>6</v>
+      </c>
+      <c r="O24" s="11">
+        <v>0</v>
+      </c>
+      <c r="P24" s="11">
+        <v>11</v>
+      </c>
+      <c r="Q24" s="11">
+        <v>4</v>
+      </c>
+      <c r="R24" s="11">
+        <v>0</v>
+      </c>
+      <c r="S24" s="11">
+        <v>0</v>
+      </c>
+      <c r="T24" s="11">
+        <v>120</v>
+      </c>
+      <c r="U24" s="11">
+        <v>330</v>
+      </c>
+      <c r="W24" s="11">
+        <v>0</v>
+      </c>
+      <c r="X24" s="11">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="11">
+        <v>8</v>
+      </c>
+      <c r="Z24" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="AA24" s="11">
+        <v>30</v>
       </c>
       <c r="AB24" s="1">
         <v>17.5</v>
@@ -10039,7 +9814,7 @@
     </row>
     <row r="25" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>218</v>
+        <v>190</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>32</v>
@@ -10047,74 +9822,74 @@
       <c r="C25" s="1">
         <v>1</v>
       </c>
-      <c r="D25" s="1" t="s">
-        <v>219</v>
+      <c r="D25" s="11">
+        <v>900</v>
       </c>
       <c r="E25" s="5">
         <v>1</v>
       </c>
-      <c r="F25" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="H25" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="J25" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="K25" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="L25" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="M25" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="N25" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="O25" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="P25" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="Q25" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="R25" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="S25" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="T25" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="U25" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="W25" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="X25" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="Y25" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="Z25" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="AA25" s="1" t="s">
-        <v>222</v>
+      <c r="F25" s="11">
+        <v>900</v>
+      </c>
+      <c r="G25" s="11">
+        <v>0</v>
+      </c>
+      <c r="H25" s="11">
+        <v>9</v>
+      </c>
+      <c r="I25" s="11">
+        <v>0</v>
+      </c>
+      <c r="J25" s="11">
+        <v>2</v>
+      </c>
+      <c r="K25" s="11">
+        <v>0</v>
+      </c>
+      <c r="L25" s="11">
+        <v>2</v>
+      </c>
+      <c r="M25" s="11">
+        <v>0</v>
+      </c>
+      <c r="N25" s="11">
+        <v>9</v>
+      </c>
+      <c r="O25" s="11">
+        <v>4</v>
+      </c>
+      <c r="P25" s="11">
+        <v>10</v>
+      </c>
+      <c r="Q25" s="11">
+        <v>4</v>
+      </c>
+      <c r="R25" s="11">
+        <v>0</v>
+      </c>
+      <c r="S25" s="11">
+        <v>0</v>
+      </c>
+      <c r="T25" s="11">
+        <v>150</v>
+      </c>
+      <c r="U25" s="11">
+        <v>363</v>
+      </c>
+      <c r="W25" s="11">
+        <v>0</v>
+      </c>
+      <c r="X25" s="11">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="11">
+        <v>9</v>
+      </c>
+      <c r="Z25" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="AA25" s="11">
+        <v>35</v>
       </c>
       <c r="AB25" s="1">
         <v>24.5</v>
@@ -10135,7 +9910,7 @@
     </row>
     <row r="26" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>223</v>
+        <v>191</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>32</v>
@@ -10143,74 +9918,74 @@
       <c r="C26" s="1">
         <v>1</v>
       </c>
-      <c r="D26" s="1" t="s">
-        <v>219</v>
+      <c r="D26" s="11">
+        <v>900</v>
       </c>
       <c r="E26" s="5">
         <v>1</v>
       </c>
-      <c r="F26" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="H26" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="J26" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="K26" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="L26" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="M26" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="N26" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="O26" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="P26" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="Q26" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="R26" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="S26" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="T26" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="U26" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="W26" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="X26" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="Y26" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="Z26" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="AA26" s="1" t="s">
-        <v>198</v>
+      <c r="F26" s="11">
+        <v>900</v>
+      </c>
+      <c r="G26" s="11">
+        <v>0</v>
+      </c>
+      <c r="H26" s="11">
+        <v>9</v>
+      </c>
+      <c r="I26" s="11">
+        <v>0</v>
+      </c>
+      <c r="J26" s="11">
+        <v>2</v>
+      </c>
+      <c r="K26" s="11">
+        <v>0</v>
+      </c>
+      <c r="L26" s="11">
+        <v>2</v>
+      </c>
+      <c r="M26" s="11">
+        <v>0</v>
+      </c>
+      <c r="N26" s="11">
+        <v>9</v>
+      </c>
+      <c r="O26" s="11">
+        <v>4</v>
+      </c>
+      <c r="P26" s="11">
+        <v>10</v>
+      </c>
+      <c r="Q26" s="11">
+        <v>4</v>
+      </c>
+      <c r="R26" s="11">
+        <v>0</v>
+      </c>
+      <c r="S26" s="11">
+        <v>0</v>
+      </c>
+      <c r="T26" s="11">
+        <v>120</v>
+      </c>
+      <c r="U26" s="11">
+        <v>323</v>
+      </c>
+      <c r="W26" s="11">
+        <v>0</v>
+      </c>
+      <c r="X26" s="11">
+        <v>0</v>
+      </c>
+      <c r="Y26" s="11">
+        <v>9</v>
+      </c>
+      <c r="Z26" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="AA26" s="11">
+        <v>30</v>
       </c>
       <c r="AB26" s="1">
         <v>24.5</v>
@@ -10231,7 +10006,7 @@
     </row>
     <row r="27" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>573</v>
+        <v>497</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>32</v>
@@ -10326,7 +10101,7 @@
     </row>
     <row r="28" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>340</v>
+        <v>264</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>32</v>
@@ -10611,7 +10386,7 @@
     </row>
     <row r="31" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>402</v>
+        <v>326</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>76</v>
@@ -10896,7 +10671,7 @@
     </row>
     <row r="34" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>444</v>
+        <v>368</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>32</v>
@@ -10991,7 +10766,7 @@
     </row>
     <row r="35" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>292</v>
+        <v>216</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>32</v>
@@ -10999,8 +10774,8 @@
       <c r="C35" s="1">
         <v>1</v>
       </c>
-      <c r="D35" s="1" t="s">
-        <v>290</v>
+      <c r="D35" s="11">
+        <v>1400</v>
       </c>
       <c r="E35" s="5">
         <v>1</v>
@@ -11088,7 +10863,7 @@
     </row>
     <row r="36" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>498</v>
+        <v>422</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>32</v>
@@ -11187,7 +10962,7 @@
     </row>
     <row r="37" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>247</v>
+        <v>198</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>32</v>
@@ -11195,75 +10970,75 @@
       <c r="C37" s="1">
         <v>1</v>
       </c>
-      <c r="D37" s="1" t="s">
-        <v>242</v>
+      <c r="D37" s="11">
+        <v>1200</v>
       </c>
       <c r="E37" s="5">
         <v>1</v>
       </c>
-      <c r="F37" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="H37" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="I37" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="J37" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="K37" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="L37" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="M37" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="N37" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="O37" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="P37" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="Q37" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="R37" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="S37" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="T37" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="U37" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="W37" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="X37" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="Y37" s="1" t="s">
-        <v>248</v>
+      <c r="F37" s="11">
+        <v>1200</v>
+      </c>
+      <c r="G37" s="11">
+        <v>0</v>
+      </c>
+      <c r="H37" s="11">
+        <v>8.5</v>
+      </c>
+      <c r="I37" s="11">
+        <v>0</v>
+      </c>
+      <c r="J37" s="11">
+        <v>3</v>
+      </c>
+      <c r="K37" s="11">
+        <v>0</v>
+      </c>
+      <c r="L37" s="11">
+        <v>2</v>
+      </c>
+      <c r="M37" s="11">
+        <v>0</v>
+      </c>
+      <c r="N37" s="11">
+        <v>6</v>
+      </c>
+      <c r="O37" s="11">
+        <v>0</v>
+      </c>
+      <c r="P37" s="11">
+        <v>15</v>
+      </c>
+      <c r="Q37" s="11">
+        <v>3</v>
+      </c>
+      <c r="R37" s="11">
+        <v>0</v>
+      </c>
+      <c r="S37" s="11">
+        <v>0</v>
+      </c>
+      <c r="T37" s="11">
+        <v>168</v>
+      </c>
+      <c r="U37" s="11">
+        <v>442</v>
+      </c>
+      <c r="W37" s="11">
+        <v>0</v>
+      </c>
+      <c r="X37" s="11">
+        <v>0</v>
+      </c>
+      <c r="Y37" s="11">
+        <v>8.5</v>
       </c>
       <c r="Z37" s="1">
         <f>8/12</f>
         <v>0.66666666666666663</v>
       </c>
-      <c r="AA37" s="1" t="s">
-        <v>252</v>
+      <c r="AA37" s="11">
+        <v>54</v>
       </c>
       <c r="AB37" s="1">
         <v>17.2</v>
@@ -11284,7 +11059,7 @@
     </row>
     <row r="38" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>271</v>
+        <v>203</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>32</v>
@@ -11292,8 +11067,8 @@
       <c r="C38" s="1">
         <v>1</v>
       </c>
-      <c r="D38" s="1" t="s">
-        <v>267</v>
+      <c r="D38" s="11">
+        <v>1250</v>
       </c>
       <c r="E38" s="5">
         <v>1</v>
@@ -11381,7 +11156,7 @@
     </row>
     <row r="39" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>274</v>
+        <v>205</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>32</v>
@@ -11389,8 +11164,8 @@
       <c r="C39" s="1">
         <v>1</v>
       </c>
-      <c r="D39" s="1" t="s">
-        <v>275</v>
+      <c r="D39" s="11">
+        <v>1300</v>
       </c>
       <c r="E39" s="5">
         <v>1</v>
@@ -11478,7 +11253,7 @@
     </row>
     <row r="40" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>283</v>
+        <v>210</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>32</v>
@@ -11486,8 +11261,8 @@
       <c r="C40" s="1">
         <v>1</v>
       </c>
-      <c r="D40" s="1" t="s">
-        <v>284</v>
+      <c r="D40" s="11">
+        <v>1375</v>
       </c>
       <c r="E40" s="5">
         <v>1</v>
@@ -11766,7 +11541,7 @@
     </row>
     <row r="43" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>608</v>
+        <v>532</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>32</v>
@@ -11958,7 +11733,7 @@
     </row>
     <row r="45" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>617</v>
+        <v>541</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>32</v>
@@ -12150,7 +11925,7 @@
     </row>
     <row r="47" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>626</v>
+        <v>550</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>32</v>
@@ -12342,7 +12117,7 @@
     </row>
     <row r="49" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>632</v>
+        <v>556</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>32</v>
@@ -12438,7 +12213,7 @@
     </row>
     <row r="50" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>516</v>
+        <v>440</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>32</v>
@@ -12533,7 +12308,7 @@
     </row>
     <row r="51" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>466</v>
+        <v>390</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>32</v>
@@ -12629,7 +12404,7 @@
     </row>
     <row r="52" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>643</v>
+        <v>567</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>32</v>
@@ -12725,7 +12500,7 @@
     </row>
     <row r="53" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>441</v>
+        <v>365</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>32</v>
@@ -12820,7 +12595,7 @@
     </row>
     <row r="54" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>446</v>
+        <v>370</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>32</v>
@@ -12915,7 +12690,7 @@
     </row>
     <row r="55" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>596</v>
+        <v>520</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>32</v>
@@ -13010,7 +12785,7 @@
     </row>
     <row r="56" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>564</v>
+        <v>488</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>32</v>
@@ -13200,7 +12975,7 @@
     </row>
     <row r="58" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>329</v>
+        <v>253</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>32</v>
@@ -13295,7 +13070,7 @@
     </row>
     <row r="59" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>371</v>
+        <v>295</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>32</v>
@@ -13390,7 +13165,7 @@
     </row>
     <row r="60" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>346</v>
+        <v>270</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>32</v>
@@ -13485,7 +13260,7 @@
     </row>
     <row r="61" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>276</v>
+        <v>206</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>32</v>
@@ -13493,8 +13268,8 @@
       <c r="C61" s="1">
         <v>1</v>
       </c>
-      <c r="D61" s="1" t="s">
-        <v>275</v>
+      <c r="D61" s="11">
+        <v>1300</v>
       </c>
       <c r="E61" s="5">
         <v>1</v>
@@ -13582,7 +13357,7 @@
     </row>
     <row r="62" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>318</v>
+        <v>242</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>32</v>
@@ -13677,7 +13452,7 @@
     </row>
     <row r="63" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>353</v>
+        <v>277</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>32</v>
@@ -13772,7 +13547,7 @@
     </row>
     <row r="64" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>499</v>
+        <v>423</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>32</v>
@@ -13871,7 +13646,7 @@
     </row>
     <row r="65" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>565</v>
+        <v>489</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>32</v>
@@ -13967,7 +13742,7 @@
     </row>
     <row r="66" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>566</v>
+        <v>490</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>32</v>
@@ -14063,7 +13838,7 @@
     </row>
     <row r="67" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>323</v>
+        <v>247</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>32</v>
@@ -14158,7 +13933,7 @@
     </row>
     <row r="68" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>504</v>
+        <v>428</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>32</v>
@@ -14257,7 +14032,7 @@
     </row>
     <row r="69" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>505</v>
+        <v>429</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>32</v>
@@ -14356,7 +14131,7 @@
     </row>
     <row r="70" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>508</v>
+        <v>432</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>32</v>
@@ -14455,7 +14230,7 @@
     </row>
     <row r="71" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>588</v>
+        <v>512</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>32</v>
@@ -14835,7 +14610,7 @@
     </row>
     <row r="75" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>599</v>
+        <v>523</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>32</v>
@@ -15025,7 +14800,7 @@
     </row>
     <row r="77" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>382</v>
+        <v>306</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>32</v>
@@ -15310,7 +15085,7 @@
     </row>
     <row r="80" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>307</v>
+        <v>231</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>32</v>
@@ -15408,7 +15183,7 @@
     </row>
     <row r="81" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>579</v>
+        <v>503</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>32</v>
@@ -15503,7 +15278,7 @@
     </row>
     <row r="82" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>339</v>
+        <v>263</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>32</v>
@@ -15598,7 +15373,7 @@
     </row>
     <row r="83" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>662</v>
+        <v>586</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>32</v>
@@ -15693,7 +15468,7 @@
     </row>
     <row r="84" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>361</v>
+        <v>285</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>32</v>
@@ -15883,7 +15658,7 @@
     </row>
     <row r="86" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>342</v>
+        <v>266</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>32</v>
@@ -15978,7 +15753,7 @@
     </row>
     <row r="87" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>360</v>
+        <v>284</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>32</v>
@@ -16169,7 +15944,7 @@
     </row>
     <row r="89" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
-        <v>604</v>
+        <v>528</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>32</v>
@@ -16265,7 +16040,7 @@
     </row>
     <row r="90" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>362</v>
+        <v>286</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>32</v>
@@ -16645,7 +16420,7 @@
     </row>
     <row r="94" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>349</v>
+        <v>273</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>32</v>
@@ -16930,7 +16705,7 @@
     </row>
     <row r="97" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>348</v>
+        <v>272</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>32</v>
@@ -17025,7 +16800,7 @@
     </row>
     <row r="98" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>600</v>
+        <v>524</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>32</v>
@@ -17120,7 +16895,7 @@
     </row>
     <row r="99" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>493</v>
+        <v>417</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>32</v>
@@ -17219,7 +16994,7 @@
     </row>
     <row r="100" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>570</v>
+        <v>494</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>32</v>
@@ -17314,7 +17089,7 @@
     </row>
     <row r="101" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>582</v>
+        <v>506</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>32</v>
@@ -17504,7 +17279,7 @@
     </row>
     <row r="103" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>557</v>
+        <v>481</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>32</v>
@@ -17694,7 +17469,7 @@
     </row>
     <row r="105" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>425</v>
+        <v>349</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>32</v>
@@ -17884,7 +17659,7 @@
     </row>
     <row r="107" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>319</v>
+        <v>243</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>32</v>
@@ -17979,7 +17754,7 @@
     </row>
     <row r="108" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>587</v>
+        <v>511</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>32</v>
@@ -18074,7 +17849,7 @@
     </row>
     <row r="109" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>597</v>
+        <v>521</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>32</v>
@@ -18169,7 +17944,7 @@
     </row>
     <row r="110" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>437</v>
+        <v>361</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>32</v>
@@ -18264,7 +18039,7 @@
     </row>
     <row r="111" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>451</v>
+        <v>375</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>32</v>
@@ -18461,7 +18236,7 @@
     </row>
     <row r="113" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="4" t="s">
-        <v>618</v>
+        <v>542</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>32</v>
@@ -18557,7 +18332,7 @@
     </row>
     <row r="114" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>513</v>
+        <v>437</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>32</v>
@@ -18652,7 +18427,7 @@
     </row>
     <row r="115" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>422</v>
+        <v>346</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>32</v>
@@ -18747,7 +18522,7 @@
     </row>
     <row r="116" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>357</v>
+        <v>281</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>32</v>
@@ -18842,7 +18617,7 @@
     </row>
     <row r="117" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>409</v>
+        <v>333</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>32</v>
@@ -18937,7 +18712,7 @@
     </row>
     <row r="118" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>236</v>
+        <v>196</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>32</v>
@@ -18945,75 +18720,75 @@
       <c r="C118" s="1">
         <v>1</v>
       </c>
-      <c r="D118" s="1" t="s">
-        <v>237</v>
+      <c r="D118" s="11">
+        <v>1100</v>
       </c>
       <c r="E118" s="5">
         <v>1</v>
       </c>
-      <c r="F118" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="G118" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="H118" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="I118" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="J118" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="K118" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="L118" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="M118" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="N118" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="O118" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="P118" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="Q118" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="R118" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="S118" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="T118" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="U118" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="W118" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="X118" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="Y118" s="1" t="s">
-        <v>203</v>
+      <c r="F118" s="11">
+        <v>1100</v>
+      </c>
+      <c r="G118" s="11">
+        <v>0</v>
+      </c>
+      <c r="H118" s="11">
+        <v>9</v>
+      </c>
+      <c r="I118" s="11">
+        <v>0</v>
+      </c>
+      <c r="J118" s="11">
+        <v>2</v>
+      </c>
+      <c r="K118" s="11">
+        <v>0</v>
+      </c>
+      <c r="L118" s="11">
+        <v>2</v>
+      </c>
+      <c r="M118" s="11">
+        <v>0</v>
+      </c>
+      <c r="N118" s="11">
+        <v>13</v>
+      </c>
+      <c r="O118" s="11">
+        <v>0</v>
+      </c>
+      <c r="P118" s="11">
+        <v>9</v>
+      </c>
+      <c r="Q118" s="11">
+        <v>3</v>
+      </c>
+      <c r="R118" s="11">
+        <v>0</v>
+      </c>
+      <c r="S118" s="11">
+        <v>0</v>
+      </c>
+      <c r="T118" s="11">
+        <v>142</v>
+      </c>
+      <c r="U118" s="11">
+        <v>348</v>
+      </c>
+      <c r="W118" s="11">
+        <v>0</v>
+      </c>
+      <c r="X118" s="11">
+        <v>0</v>
+      </c>
+      <c r="Y118" s="11">
+        <v>9</v>
       </c>
       <c r="Z118" s="1">
         <f>8/12</f>
         <v>0.66666666666666663</v>
       </c>
-      <c r="AA118" s="1" t="s">
-        <v>206</v>
+      <c r="AA118" s="11">
+        <v>33</v>
       </c>
       <c r="AB118" s="1">
         <v>21.8</v>
@@ -19034,7 +18809,7 @@
     </row>
     <row r="119" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>462</v>
+        <v>386</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>32</v>
@@ -19129,7 +18904,7 @@
     </row>
     <row r="120" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>396</v>
+        <v>320</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>32</v>
@@ -19415,7 +19190,7 @@
     </row>
     <row r="123" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="4" t="s">
-        <v>621</v>
+        <v>545</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>32</v>
@@ -19511,7 +19286,7 @@
     </row>
     <row r="124" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>312</v>
+        <v>236</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>76</v>
@@ -19609,7 +19384,7 @@
     </row>
     <row r="125" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>200</v>
+        <v>187</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>32</v>
@@ -19617,74 +19392,74 @@
       <c r="C125" s="1">
         <v>1</v>
       </c>
-      <c r="D125" s="1" t="s">
-        <v>201</v>
+      <c r="D125" s="11">
+        <v>950</v>
       </c>
       <c r="E125" s="5">
         <v>1</v>
       </c>
-      <c r="F125" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="G125" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="H125" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="I125" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="J125" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="K125" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="L125" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="M125" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="N125" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="O125" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="P125" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="Q125" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="R125" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="S125" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="T125" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="U125" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="W125" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="X125" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="Y125" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="Z125" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="AA125" s="1" t="s">
-        <v>206</v>
+      <c r="F125" s="11">
+        <v>950</v>
+      </c>
+      <c r="G125" s="11">
+        <v>0</v>
+      </c>
+      <c r="H125" s="11">
+        <v>8</v>
+      </c>
+      <c r="I125" s="11">
+        <v>0</v>
+      </c>
+      <c r="J125" s="11">
+        <v>2</v>
+      </c>
+      <c r="K125" s="11">
+        <v>0</v>
+      </c>
+      <c r="L125" s="11">
+        <v>1</v>
+      </c>
+      <c r="M125" s="11">
+        <v>0</v>
+      </c>
+      <c r="N125" s="11">
+        <v>7</v>
+      </c>
+      <c r="O125" s="11">
+        <v>0</v>
+      </c>
+      <c r="P125" s="11">
+        <v>9</v>
+      </c>
+      <c r="Q125" s="11">
+        <v>3</v>
+      </c>
+      <c r="R125" s="11">
+        <v>0</v>
+      </c>
+      <c r="S125" s="11">
+        <v>0</v>
+      </c>
+      <c r="T125" s="11">
+        <v>136</v>
+      </c>
+      <c r="U125" s="11">
+        <v>272</v>
+      </c>
+      <c r="W125" s="11">
+        <v>0</v>
+      </c>
+      <c r="X125" s="11">
+        <v>0</v>
+      </c>
+      <c r="Y125" s="11">
+        <v>8</v>
+      </c>
+      <c r="Z125" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="AA125" s="11">
+        <v>33</v>
       </c>
       <c r="AB125" s="1">
         <v>21.5</v>
@@ -19990,7 +19765,7 @@
     </row>
     <row r="129" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>324</v>
+        <v>248</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>32</v>
@@ -20085,7 +19860,7 @@
     </row>
     <row r="130" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>590</v>
+        <v>514</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>32</v>
@@ -20275,7 +20050,7 @@
     </row>
     <row r="132" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
-        <v>366</v>
+        <v>290</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>32</v>
@@ -20465,7 +20240,7 @@
     </row>
     <row r="134" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
-        <v>272</v>
+        <v>204</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>32</v>
@@ -20473,8 +20248,8 @@
       <c r="C134" s="1">
         <v>1</v>
       </c>
-      <c r="D134" s="1" t="s">
-        <v>273</v>
+      <c r="D134" s="11">
+        <v>1251</v>
       </c>
       <c r="E134" s="5">
         <v>1</v>
@@ -20753,7 +20528,7 @@
     </row>
     <row r="137" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="4" t="s">
-        <v>616</v>
+        <v>540</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>32</v>
@@ -20849,7 +20624,7 @@
     </row>
     <row r="138" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
-        <v>380</v>
+        <v>304</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>32</v>
@@ -21039,7 +20814,7 @@
     </row>
     <row r="140" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
-        <v>464</v>
+        <v>388</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>32</v>
@@ -21229,7 +21004,7 @@
     </row>
     <row r="142" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
-        <v>391</v>
+        <v>315</v>
       </c>
       <c r="B142" s="1" t="s">
         <v>32</v>
@@ -21324,7 +21099,7 @@
     </row>
     <row r="143" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="4" t="s">
-        <v>463</v>
+        <v>387</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>32</v>
@@ -21420,7 +21195,7 @@
     </row>
     <row r="144" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>642</v>
+        <v>566</v>
       </c>
       <c r="B144" s="1" t="s">
         <v>32</v>
@@ -21516,7 +21291,7 @@
     </row>
     <row r="145" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
-        <v>545</v>
+        <v>469</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>32</v>
@@ -21611,7 +21386,7 @@
     </row>
     <row r="146" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>486</v>
+        <v>410</v>
       </c>
       <c r="B146" s="1" t="s">
         <v>32</v>
@@ -21707,7 +21482,7 @@
     </row>
     <row r="147" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="4" t="s">
-        <v>660</v>
+        <v>584</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>32</v>
@@ -21803,7 +21578,7 @@
     </row>
     <row r="148" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
-        <v>440</v>
+        <v>364</v>
       </c>
       <c r="B148" s="1" t="s">
         <v>32</v>
@@ -21898,7 +21673,7 @@
     </row>
     <row r="149" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>322</v>
+        <v>246</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>32</v>
@@ -22088,7 +21863,7 @@
     </row>
     <row r="151" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
-        <v>668</v>
+        <v>592</v>
       </c>
       <c r="B151" s="1" t="s">
         <v>32</v>
@@ -22278,7 +22053,7 @@
     </row>
     <row r="153" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="4" t="s">
-        <v>574</v>
+        <v>498</v>
       </c>
       <c r="B153" s="1" t="s">
         <v>32</v>
@@ -22374,7 +22149,7 @@
     </row>
     <row r="154" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>575</v>
+        <v>499</v>
       </c>
       <c r="B154" s="1" t="s">
         <v>32</v>
@@ -22470,7 +22245,7 @@
     </row>
     <row r="155" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
-        <v>383</v>
+        <v>307</v>
       </c>
       <c r="B155" s="1" t="s">
         <v>32</v>
@@ -22565,7 +22340,7 @@
     </row>
     <row r="156" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
-        <v>543</v>
+        <v>467</v>
       </c>
       <c r="B156" s="1" t="s">
         <v>32</v>
@@ -22660,7 +22435,7 @@
     </row>
     <row r="157" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
-        <v>355</v>
+        <v>279</v>
       </c>
       <c r="B157" s="1" t="s">
         <v>32</v>
@@ -22755,7 +22530,7 @@
     </row>
     <row r="158" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
-        <v>373</v>
+        <v>297</v>
       </c>
       <c r="B158" s="1" t="s">
         <v>32</v>
@@ -22850,7 +22625,7 @@
     </row>
     <row r="159" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="4" t="s">
-        <v>474</v>
+        <v>398</v>
       </c>
       <c r="B159" s="1" t="s">
         <v>32</v>
@@ -22946,7 +22721,7 @@
     </row>
     <row r="160" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
-        <v>649</v>
+        <v>573</v>
       </c>
       <c r="B160" s="1" t="s">
         <v>32</v>
@@ -23042,7 +22817,7 @@
     </row>
     <row r="161" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
-        <v>289</v>
+        <v>213</v>
       </c>
       <c r="B161" s="1" t="s">
         <v>32</v>
@@ -23050,8 +22825,8 @@
       <c r="C161" s="1">
         <v>1</v>
       </c>
-      <c r="D161" s="1" t="s">
-        <v>290</v>
+      <c r="D161" s="11">
+        <v>1400</v>
       </c>
       <c r="E161" s="5">
         <v>1</v>
@@ -23139,7 +22914,7 @@
     </row>
     <row r="162" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
-        <v>549</v>
+        <v>473</v>
       </c>
       <c r="B162" s="1" t="s">
         <v>32</v>
@@ -23425,7 +23200,7 @@
     </row>
     <row r="165" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
-        <v>302</v>
+        <v>226</v>
       </c>
       <c r="B165" s="1" t="s">
         <v>32</v>
@@ -23523,7 +23298,7 @@
     </row>
     <row r="166" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
-        <v>404</v>
+        <v>328</v>
       </c>
       <c r="B166" s="1" t="s">
         <v>32</v>
@@ -23618,7 +23393,7 @@
     </row>
     <row r="167" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
-        <v>310</v>
+        <v>234</v>
       </c>
       <c r="B167" s="1" t="s">
         <v>32</v>
@@ -23715,7 +23490,7 @@
     </row>
     <row r="168" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
-        <v>467</v>
+        <v>391</v>
       </c>
       <c r="B168" s="1" t="s">
         <v>32</v>
@@ -23811,7 +23586,7 @@
     </row>
     <row r="169" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="4" t="s">
-        <v>644</v>
+        <v>568</v>
       </c>
       <c r="B169" s="1" t="s">
         <v>32</v>
@@ -24002,7 +23777,7 @@
     </row>
     <row r="171" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
-        <v>423</v>
+        <v>347</v>
       </c>
       <c r="B171" s="1" t="s">
         <v>32</v>
@@ -24097,7 +23872,7 @@
     </row>
     <row r="172" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
-        <v>452</v>
+        <v>376</v>
       </c>
       <c r="B172" s="1" t="s">
         <v>32</v>
@@ -24196,7 +23971,7 @@
     </row>
     <row r="173" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
-        <v>560</v>
+        <v>484</v>
       </c>
       <c r="B173" s="1" t="s">
         <v>32</v>
@@ -24387,7 +24162,7 @@
     </row>
     <row r="175" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="4" t="s">
-        <v>609</v>
+        <v>533</v>
       </c>
       <c r="B175" s="1" t="s">
         <v>32</v>
@@ -24483,7 +24258,7 @@
     </row>
     <row r="176" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
-        <v>395</v>
+        <v>319</v>
       </c>
       <c r="B176" s="1" t="s">
         <v>32</v>
@@ -24673,7 +24448,7 @@
     </row>
     <row r="178" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="4" t="s">
-        <v>473</v>
+        <v>397</v>
       </c>
       <c r="B178" s="1" t="s">
         <v>32</v>
@@ -24769,7 +24544,7 @@
     </row>
     <row r="179" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="4" t="s">
-        <v>648</v>
+        <v>572</v>
       </c>
       <c r="B179" s="1" t="s">
         <v>32</v>
@@ -24960,7 +24735,7 @@
     </row>
     <row r="181" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
-        <v>397</v>
+        <v>321</v>
       </c>
       <c r="B181" s="1" t="s">
         <v>32</v>
@@ -25055,7 +24830,7 @@
     </row>
     <row r="182" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="4" t="s">
-        <v>583</v>
+        <v>507</v>
       </c>
       <c r="B182" s="1" t="s">
         <v>32</v>
@@ -25151,7 +24926,7 @@
     </row>
     <row r="183" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="4" t="s">
-        <v>584</v>
+        <v>508</v>
       </c>
       <c r="B183" s="1" t="s">
         <v>32</v>
@@ -25247,7 +25022,7 @@
     </row>
     <row r="184" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
-        <v>335</v>
+        <v>259</v>
       </c>
       <c r="B184" s="1" t="s">
         <v>32</v>
@@ -25437,7 +25212,7 @@
     </row>
     <row r="186" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
-        <v>354</v>
+        <v>278</v>
       </c>
       <c r="B186" s="1" t="s">
         <v>32</v>
@@ -25532,7 +25307,7 @@
     </row>
     <row r="187" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
-        <v>561</v>
+        <v>485</v>
       </c>
       <c r="B187" s="1" t="s">
         <v>32</v>
@@ -25723,7 +25498,7 @@
     </row>
     <row r="189" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="4" t="s">
-        <v>605</v>
+        <v>529</v>
       </c>
       <c r="B189" s="1" t="s">
         <v>32</v>
@@ -25914,7 +25689,7 @@
     </row>
     <row r="191" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
-        <v>408</v>
+        <v>332</v>
       </c>
       <c r="B191" s="1" t="s">
         <v>32</v>
@@ -26105,7 +25880,7 @@
     </row>
     <row r="193" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="4" t="s">
-        <v>638</v>
+        <v>562</v>
       </c>
       <c r="B193" s="1" t="s">
         <v>32</v>
@@ -26201,7 +25976,7 @@
     </row>
     <row r="194" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
-        <v>530</v>
+        <v>454</v>
       </c>
       <c r="B194" s="1" t="s">
         <v>32</v>
@@ -26296,7 +26071,7 @@
     </row>
     <row r="195" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
-        <v>433</v>
+        <v>357</v>
       </c>
       <c r="B195" s="1" t="s">
         <v>32</v>
@@ -26391,7 +26166,7 @@
     </row>
     <row r="196" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
-        <v>443</v>
+        <v>367</v>
       </c>
       <c r="B196" s="1" t="s">
         <v>32</v>
@@ -26486,7 +26261,7 @@
     </row>
     <row r="197" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
-        <v>547</v>
+        <v>471</v>
       </c>
       <c r="B197" s="1" t="s">
         <v>32</v>
@@ -26581,7 +26356,7 @@
     </row>
     <row r="198" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
-        <v>341</v>
+        <v>265</v>
       </c>
       <c r="B198" s="1" t="s">
         <v>32</v>
@@ -26676,7 +26451,7 @@
     </row>
     <row r="199" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
-        <v>372</v>
+        <v>296</v>
       </c>
       <c r="B199" s="1" t="s">
         <v>32</v>
@@ -26771,7 +26546,7 @@
     </row>
     <row r="200" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
-        <v>315</v>
+        <v>239</v>
       </c>
       <c r="B200" s="1" t="s">
         <v>32</v>
@@ -26962,7 +26737,7 @@
     </row>
     <row r="202" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="4" t="s">
-        <v>627</v>
+        <v>551</v>
       </c>
       <c r="B202" s="1" t="s">
         <v>32</v>
@@ -27154,7 +26929,7 @@
     </row>
     <row r="204" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="4" t="s">
-        <v>612</v>
+        <v>536</v>
       </c>
       <c r="B204" s="1" t="s">
         <v>32</v>
@@ -27250,7 +27025,7 @@
     </row>
     <row r="205" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
-        <v>374</v>
+        <v>298</v>
       </c>
       <c r="B205" s="1" t="s">
         <v>32</v>
@@ -27535,7 +27310,7 @@
     </row>
     <row r="208" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
-        <v>527</v>
+        <v>451</v>
       </c>
       <c r="B208" s="1" t="s">
         <v>32</v>
@@ -27630,7 +27405,7 @@
     </row>
     <row r="209" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="4" t="s">
-        <v>580</v>
+        <v>504</v>
       </c>
       <c r="B209" s="1" t="s">
         <v>32</v>
@@ -27726,7 +27501,7 @@
     </row>
     <row r="210" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="4" t="s">
-        <v>581</v>
+        <v>505</v>
       </c>
       <c r="B210" s="1" t="s">
         <v>32</v>
@@ -27822,7 +27597,7 @@
     </row>
     <row r="211" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
-        <v>333</v>
+        <v>257</v>
       </c>
       <c r="B211" s="1" t="s">
         <v>32</v>
@@ -27917,7 +27692,7 @@
     </row>
     <row r="212" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
-        <v>663</v>
+        <v>587</v>
       </c>
       <c r="B212" s="1" t="s">
         <v>32</v>
@@ -28107,7 +27882,7 @@
     </row>
     <row r="214" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
-        <v>316</v>
+        <v>240</v>
       </c>
       <c r="B214" s="1" t="s">
         <v>32</v>
@@ -28202,7 +27977,7 @@
     </row>
     <row r="215" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
-        <v>515</v>
+        <v>439</v>
       </c>
       <c r="B215" s="1" t="s">
         <v>32</v>
@@ -28297,7 +28072,7 @@
     </row>
     <row r="216" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
-        <v>521</v>
+        <v>445</v>
       </c>
       <c r="B216" s="1" t="s">
         <v>32</v>
@@ -28392,7 +28167,7 @@
     </row>
     <row r="217" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
-        <v>528</v>
+        <v>452</v>
       </c>
       <c r="B217" s="1" t="s">
         <v>32</v>
@@ -28487,7 +28262,7 @@
     </row>
     <row r="218" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="4" t="s">
-        <v>471</v>
+        <v>395</v>
       </c>
       <c r="B218" s="1" t="s">
         <v>32</v>
@@ -28583,7 +28358,7 @@
     </row>
     <row r="219" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="4" t="s">
-        <v>647</v>
+        <v>571</v>
       </c>
       <c r="B219" s="1" t="s">
         <v>32</v>
@@ -28679,7 +28454,7 @@
     </row>
     <row r="220" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
-        <v>378</v>
+        <v>302</v>
       </c>
       <c r="B220" s="1" t="s">
         <v>32</v>
@@ -28965,7 +28740,7 @@
     </row>
     <row r="223" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="4" t="s">
-        <v>615</v>
+        <v>539</v>
       </c>
       <c r="B223" s="1" t="s">
         <v>32</v>
@@ -29252,7 +29027,7 @@
     </row>
     <row r="226" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="4" t="s">
-        <v>619</v>
+        <v>543</v>
       </c>
       <c r="B226" s="1" t="s">
         <v>32</v>
@@ -29444,7 +29219,7 @@
     </row>
     <row r="228" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="4" t="s">
-        <v>622</v>
+        <v>546</v>
       </c>
       <c r="B228" s="1" t="s">
         <v>32</v>
@@ -29540,7 +29315,7 @@
     </row>
     <row r="229" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
-        <v>403</v>
+        <v>327</v>
       </c>
       <c r="B229" s="1" t="s">
         <v>32</v>
@@ -29635,7 +29410,7 @@
     </row>
     <row r="230" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
-        <v>375</v>
+        <v>299</v>
       </c>
       <c r="B230" s="1" t="s">
         <v>32</v>
@@ -29921,7 +29696,7 @@
     </row>
     <row r="233" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="4" t="s">
-        <v>634</v>
+        <v>558</v>
       </c>
       <c r="B233" s="1" t="s">
         <v>32</v>
@@ -30017,7 +29792,7 @@
     </row>
     <row r="234" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
-        <v>417</v>
+        <v>341</v>
       </c>
       <c r="B234" s="1" t="s">
         <v>32</v>
@@ -30112,7 +29887,7 @@
     </row>
     <row r="235" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
-        <v>356</v>
+        <v>280</v>
       </c>
       <c r="B235" s="1" t="s">
         <v>32</v>
@@ -30398,7 +30173,7 @@
     </row>
     <row r="238" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="4" t="s">
-        <v>633</v>
+        <v>557</v>
       </c>
       <c r="B238" s="1" t="s">
         <v>32</v>
@@ -30494,7 +30269,7 @@
     </row>
     <row r="239" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
-        <v>406</v>
+        <v>330</v>
       </c>
       <c r="B239" s="9" t="s">
         <v>32</v>
@@ -30590,7 +30365,7 @@
     </row>
     <row r="240" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
-        <v>519</v>
+        <v>443</v>
       </c>
       <c r="B240" s="1" t="s">
         <v>32</v>
@@ -30685,7 +30460,7 @@
     </row>
     <row r="241" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
-        <v>412</v>
+        <v>336</v>
       </c>
       <c r="B241" s="1" t="s">
         <v>32</v>
@@ -30780,7 +30555,7 @@
     </row>
     <row r="242" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
-        <v>536</v>
+        <v>460</v>
       </c>
       <c r="B242" s="1" t="s">
         <v>32</v>
@@ -30875,7 +30650,7 @@
     </row>
     <row r="243" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
-        <v>435</v>
+        <v>359</v>
       </c>
       <c r="B243" s="1" t="s">
         <v>32</v>
@@ -30970,7 +30745,7 @@
     </row>
     <row r="244" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
-        <v>281</v>
+        <v>209</v>
       </c>
       <c r="B244" s="1" t="s">
         <v>32</v>
@@ -30978,8 +30753,8 @@
       <c r="C244" s="1">
         <v>1</v>
       </c>
-      <c r="D244" s="1" t="s">
-        <v>282</v>
+      <c r="D244" s="11">
+        <v>1354</v>
       </c>
       <c r="E244" s="5">
         <v>1</v>
@@ -31067,7 +30842,7 @@
     </row>
     <row r="245" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
-        <v>523</v>
+        <v>447</v>
       </c>
       <c r="B245" s="1" t="s">
         <v>76</v>
@@ -31162,7 +30937,7 @@
     </row>
     <row r="246" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
-        <v>253</v>
+        <v>199</v>
       </c>
       <c r="B246" s="1" t="s">
         <v>32</v>
@@ -31170,74 +30945,74 @@
       <c r="C246" s="1">
         <v>1</v>
       </c>
-      <c r="D246" s="1" t="s">
-        <v>242</v>
+      <c r="D246" s="11">
+        <v>1200</v>
       </c>
       <c r="E246" s="5">
         <v>1</v>
       </c>
-      <c r="F246" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="G246" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="H246" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="I246" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="J246" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="K246" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="L246" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="M246" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="N246" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="O246" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="P246" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="Q246" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="R246" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="S246" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="T246" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="U246" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="W246" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="X246" s="1" t="s">
-        <v>188</v>
+      <c r="F246" s="11">
+        <v>1200</v>
+      </c>
+      <c r="G246" s="11">
+        <v>0</v>
+      </c>
+      <c r="H246" s="11">
+        <v>8</v>
+      </c>
+      <c r="I246" s="11">
+        <v>0</v>
+      </c>
+      <c r="J246" s="11">
+        <v>3</v>
+      </c>
+      <c r="K246" s="11">
+        <v>0</v>
+      </c>
+      <c r="L246" s="11">
+        <v>2</v>
+      </c>
+      <c r="M246" s="11">
+        <v>0</v>
+      </c>
+      <c r="N246" s="11">
+        <v>8</v>
+      </c>
+      <c r="O246" s="11">
+        <v>0</v>
+      </c>
+      <c r="P246" s="11">
+        <v>11</v>
+      </c>
+      <c r="Q246" s="11">
+        <v>4</v>
+      </c>
+      <c r="R246" s="11">
+        <v>0</v>
+      </c>
+      <c r="S246" s="11">
+        <v>0</v>
+      </c>
+      <c r="T246" s="11">
+        <v>186</v>
+      </c>
+      <c r="U246" s="11">
+        <v>409</v>
+      </c>
+      <c r="W246" s="11">
+        <v>0</v>
+      </c>
+      <c r="X246" s="11">
+        <v>0</v>
       </c>
       <c r="Y246" s="1">
         <v>8</v>
       </c>
-      <c r="Z246" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="AA246" s="1" t="s">
-        <v>256</v>
+      <c r="Z246" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="AA246" s="11">
+        <v>60</v>
       </c>
       <c r="AB246" s="1">
         <v>15.3</v>
@@ -31353,7 +31128,7 @@
     </row>
     <row r="248" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="9" t="s">
-        <v>477</v>
+        <v>401</v>
       </c>
       <c r="B248" s="1" t="s">
         <v>32</v>
@@ -31828,7 +31603,7 @@
     </row>
     <row r="253" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="s">
-        <v>363</v>
+        <v>287</v>
       </c>
       <c r="B253" s="1" t="s">
         <v>32</v>
@@ -31923,7 +31698,7 @@
     </row>
     <row r="254" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="s">
-        <v>400</v>
+        <v>324</v>
       </c>
       <c r="B254" s="1" t="s">
         <v>32</v>
@@ -32018,7 +31793,7 @@
     </row>
     <row r="255" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
-        <v>529</v>
+        <v>453</v>
       </c>
       <c r="B255" s="1" t="s">
         <v>32</v>
@@ -32113,7 +31888,7 @@
     </row>
     <row r="256" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="1" t="s">
-        <v>585</v>
+        <v>509</v>
       </c>
       <c r="B256" s="1" t="s">
         <v>32</v>
@@ -32208,7 +31983,7 @@
     </row>
     <row r="257" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
-        <v>336</v>
+        <v>260</v>
       </c>
       <c r="B257" s="1" t="s">
         <v>32</v>
@@ -32303,7 +32078,7 @@
     </row>
     <row r="258" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
-        <v>343</v>
+        <v>267</v>
       </c>
       <c r="B258" s="1" t="s">
         <v>32</v>
@@ -32398,7 +32173,7 @@
     </row>
     <row r="259" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
-        <v>520</v>
+        <v>444</v>
       </c>
       <c r="B259" s="1" t="s">
         <v>32</v>
@@ -32493,7 +32268,7 @@
     </row>
     <row r="260" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
-        <v>277</v>
+        <v>207</v>
       </c>
       <c r="B260" s="1" t="s">
         <v>32</v>
@@ -32501,8 +32276,8 @@
       <c r="C260" s="1">
         <v>1</v>
       </c>
-      <c r="D260" s="1" t="s">
-        <v>278</v>
+      <c r="D260" s="11">
+        <v>1310</v>
       </c>
       <c r="E260" s="5">
         <v>1</v>
@@ -32685,7 +32460,7 @@
     </row>
     <row r="262" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
-        <v>330</v>
+        <v>254</v>
       </c>
       <c r="B262" s="1" t="s">
         <v>32</v>
@@ -32780,7 +32555,7 @@
     </row>
     <row r="263" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
-        <v>511</v>
+        <v>435</v>
       </c>
       <c r="B263" s="1" t="s">
         <v>32</v>
@@ -33165,7 +32940,7 @@
     </row>
     <row r="267" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="4" t="s">
-        <v>624</v>
+        <v>548</v>
       </c>
       <c r="B267" s="1" t="s">
         <v>32</v>
@@ -33261,7 +33036,7 @@
     </row>
     <row r="268" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
-        <v>392</v>
+        <v>316</v>
       </c>
       <c r="B268" s="1" t="s">
         <v>32</v>
@@ -33356,7 +33131,7 @@
     </row>
     <row r="269" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="1" t="s">
-        <v>489</v>
+        <v>413</v>
       </c>
       <c r="B269" s="1" t="s">
         <v>32</v>
@@ -33451,10 +33226,10 @@
     </row>
     <row r="270" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="1" t="s">
-        <v>447</v>
+        <v>371</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>667</v>
+        <v>591</v>
       </c>
       <c r="C270" s="1">
         <v>1</v>
@@ -33546,10 +33321,10 @@
     </row>
     <row r="271" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
-        <v>448</v>
+        <v>372</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>667</v>
+        <v>591</v>
       </c>
       <c r="C271" s="1">
         <v>1</v>
@@ -33736,7 +33511,7 @@
     </row>
     <row r="273" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
-        <v>598</v>
+        <v>522</v>
       </c>
       <c r="B273" s="1" t="s">
         <v>32</v>
@@ -33926,7 +33701,7 @@
     </row>
     <row r="275" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="1" t="s">
-        <v>358</v>
+        <v>282</v>
       </c>
       <c r="B275" s="1" t="s">
         <v>32</v>
@@ -34211,7 +33986,7 @@
     </row>
     <row r="278" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="1" t="s">
-        <v>398</v>
+        <v>322</v>
       </c>
       <c r="B278" s="1" t="s">
         <v>32</v>
@@ -34306,7 +34081,7 @@
     </row>
     <row r="279" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
-        <v>410</v>
+        <v>334</v>
       </c>
       <c r="B279" s="1" t="s">
         <v>32</v>
@@ -34401,7 +34176,7 @@
     </row>
     <row r="280" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
-        <v>531</v>
+        <v>455</v>
       </c>
       <c r="B280" s="1" t="s">
         <v>32</v>
@@ -34496,7 +34271,7 @@
     </row>
     <row r="281" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="4" t="s">
-        <v>484</v>
+        <v>408</v>
       </c>
       <c r="B281" s="1" t="s">
         <v>32</v>
@@ -34592,7 +34367,7 @@
     </row>
     <row r="282" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="4" t="s">
-        <v>658</v>
+        <v>582</v>
       </c>
       <c r="B282" s="1" t="s">
         <v>32</v>
@@ -34688,7 +34463,7 @@
     </row>
     <row r="283" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="1" t="s">
-        <v>257</v>
+        <v>200</v>
       </c>
       <c r="B283" s="1" t="s">
         <v>32</v>
@@ -34696,74 +34471,74 @@
       <c r="C283" s="1">
         <v>1</v>
       </c>
-      <c r="D283" s="1" t="s">
-        <v>258</v>
+      <c r="D283" s="11">
+        <v>1216</v>
       </c>
       <c r="E283" s="5">
         <v>1</v>
       </c>
-      <c r="F283" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="G283" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="H283" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="I283" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="J283" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="K283" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="L283" s="1" t="s">
+      <c r="F283" s="11">
+        <v>1216</v>
+      </c>
+      <c r="G283" s="11">
+        <v>0</v>
+      </c>
+      <c r="H283" s="11">
+        <v>8</v>
+      </c>
+      <c r="I283" s="11">
+        <v>0</v>
+      </c>
+      <c r="J283" s="11">
+        <v>3</v>
+      </c>
+      <c r="K283" s="11">
+        <v>0</v>
+      </c>
+      <c r="L283" s="11">
+        <v>2</v>
+      </c>
+      <c r="M283" s="11">
+        <v>0</v>
+      </c>
+      <c r="N283" s="11">
+        <v>8</v>
+      </c>
+      <c r="O283" s="11">
+        <v>0</v>
+      </c>
+      <c r="P283" s="11">
+        <v>11</v>
+      </c>
+      <c r="Q283" s="11">
+        <v>4</v>
+      </c>
+      <c r="R283" s="11">
+        <v>0</v>
+      </c>
+      <c r="S283" s="11">
+        <v>0</v>
+      </c>
+      <c r="T283" s="11">
         <v>194</v>
       </c>
-      <c r="M283" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="N283" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="O283" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="P283" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="Q283" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="R283" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="S283" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="T283" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="U283" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="W283" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="X283" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="Y283" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="Z283" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="AA283" s="1" t="s">
-        <v>261</v>
+      <c r="U283" s="11">
+        <v>441</v>
+      </c>
+      <c r="W283" s="11">
+        <v>0</v>
+      </c>
+      <c r="X283" s="11">
+        <v>0</v>
+      </c>
+      <c r="Y283" s="11">
+        <v>8</v>
+      </c>
+      <c r="Z283" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="AA283" s="11">
+        <v>62</v>
       </c>
       <c r="AB283" s="1">
         <v>15.3</v>
@@ -35165,7 +34940,7 @@
     </row>
     <row r="288" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="4" t="s">
-        <v>613</v>
+        <v>537</v>
       </c>
       <c r="B288" s="1" t="s">
         <v>32</v>
@@ -35357,7 +35132,7 @@
     </row>
     <row r="290" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="4" t="s">
-        <v>625</v>
+        <v>549</v>
       </c>
       <c r="B290" s="1" t="s">
         <v>32</v>
@@ -35453,7 +35228,7 @@
     </row>
     <row r="291" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="1" t="s">
-        <v>413</v>
+        <v>337</v>
       </c>
       <c r="B291" s="1" t="s">
         <v>32</v>
@@ -35644,7 +35419,7 @@
     </row>
     <row r="293" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="4" t="s">
-        <v>639</v>
+        <v>563</v>
       </c>
       <c r="B293" s="1" t="s">
         <v>32</v>
@@ -35740,7 +35515,7 @@
     </row>
     <row r="294" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="1" t="s">
-        <v>420</v>
+        <v>344</v>
       </c>
       <c r="B294" s="1" t="s">
         <v>32</v>
@@ -35835,7 +35610,7 @@
     </row>
     <row r="295" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="4" t="s">
-        <v>469</v>
+        <v>393</v>
       </c>
       <c r="B295" s="1" t="s">
         <v>32</v>
@@ -35931,7 +35706,7 @@
     </row>
     <row r="296" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="4" t="s">
-        <v>646</v>
+        <v>570</v>
       </c>
       <c r="B296" s="1" t="s">
         <v>32</v>
@@ -36027,7 +35802,7 @@
     </row>
     <row r="297" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="1" t="s">
-        <v>470</v>
+        <v>394</v>
       </c>
       <c r="B297" s="1" t="s">
         <v>32</v>
@@ -36217,7 +35992,7 @@
     </row>
     <row r="299" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="1" t="s">
-        <v>601</v>
+        <v>525</v>
       </c>
       <c r="B299" s="1" t="s">
         <v>32</v>
@@ -36312,7 +36087,7 @@
     </row>
     <row r="300" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="1" t="s">
-        <v>337</v>
+        <v>261</v>
       </c>
       <c r="B300" s="1" t="s">
         <v>32</v>
@@ -36503,7 +36278,7 @@
     </row>
     <row r="302" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="4" t="s">
-        <v>603</v>
+        <v>527</v>
       </c>
       <c r="B302" s="1" t="s">
         <v>32</v>
@@ -36790,7 +36565,7 @@
     </row>
     <row r="305" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" s="4" t="s">
-        <v>606</v>
+        <v>530</v>
       </c>
       <c r="B305" s="1" t="s">
         <v>32</v>
@@ -36886,7 +36661,7 @@
     </row>
     <row r="306" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="1" t="s">
-        <v>377</v>
+        <v>301</v>
       </c>
       <c r="B306" s="1" t="s">
         <v>32</v>
@@ -36981,7 +36756,7 @@
     </row>
     <row r="307" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="1" t="s">
-        <v>384</v>
+        <v>308</v>
       </c>
       <c r="B307" s="1" t="s">
         <v>32</v>
@@ -37172,7 +36947,7 @@
     </row>
     <row r="309" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="4" t="s">
-        <v>611</v>
+        <v>535</v>
       </c>
       <c r="B309" s="1" t="s">
         <v>32</v>
@@ -37363,7 +37138,7 @@
     </row>
     <row r="311" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="1" t="s">
-        <v>488</v>
+        <v>412</v>
       </c>
       <c r="B311" s="1" t="s">
         <v>32</v>
@@ -37458,7 +37233,7 @@
     </row>
     <row r="312" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="1" t="s">
-        <v>665</v>
+        <v>589</v>
       </c>
       <c r="B312" s="1" t="s">
         <v>32</v>
@@ -37553,7 +37328,7 @@
     </row>
     <row r="313" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" s="1" t="s">
-        <v>350</v>
+        <v>274</v>
       </c>
       <c r="B313" s="1" t="s">
         <v>32</v>
@@ -37743,7 +37518,7 @@
     </row>
     <row r="315" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" s="1" t="s">
-        <v>518</v>
+        <v>442</v>
       </c>
       <c r="B315" s="1" t="s">
         <v>32</v>
@@ -37838,7 +37613,7 @@
     </row>
     <row r="316" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" s="4" t="s">
-        <v>593</v>
+        <v>517</v>
       </c>
       <c r="B316" s="1" t="s">
         <v>32</v>
@@ -37934,7 +37709,7 @@
     </row>
     <row r="317" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A317" s="4" t="s">
-        <v>594</v>
+        <v>518</v>
       </c>
       <c r="B317" s="1" t="s">
         <v>32</v>
@@ -38315,7 +38090,7 @@
     </row>
     <row r="321" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A321" s="1" t="s">
-        <v>314</v>
+        <v>238</v>
       </c>
       <c r="B321" s="1" t="s">
         <v>76</v>
@@ -38410,7 +38185,7 @@
     </row>
     <row r="322" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A322" s="1" t="s">
-        <v>338</v>
+        <v>262</v>
       </c>
       <c r="B322" s="1" t="s">
         <v>32</v>
@@ -38600,7 +38375,7 @@
     </row>
     <row r="324" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A324" s="1" t="s">
-        <v>389</v>
+        <v>313</v>
       </c>
       <c r="B324" s="1" t="s">
         <v>32</v>
@@ -38790,7 +38565,7 @@
     </row>
     <row r="326" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326" s="1" t="s">
-        <v>230</v>
+        <v>195</v>
       </c>
       <c r="B326" s="1" t="s">
         <v>32</v>
@@ -38798,74 +38573,74 @@
       <c r="C326" s="1">
         <v>1</v>
       </c>
-      <c r="D326" s="1" t="s">
-        <v>231</v>
+      <c r="D326" s="11">
+        <v>1233</v>
       </c>
       <c r="E326" s="5">
         <v>1</v>
       </c>
-      <c r="F326" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="G326" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="H326" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="I326" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="J326" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="K326" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="L326" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="M326" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="N326" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="O326" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="P326" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="Q326" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="R326" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="S326" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="T326" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="U326" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="W326" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="X326" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="Y326" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="Z326" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="AA326" s="1" t="s">
-        <v>187</v>
+      <c r="F326" s="11">
+        <v>1016</v>
+      </c>
+      <c r="G326" s="11">
+        <v>217</v>
+      </c>
+      <c r="H326" s="11">
+        <v>8</v>
+      </c>
+      <c r="I326" s="11">
+        <v>4</v>
+      </c>
+      <c r="J326" s="11">
+        <v>2</v>
+      </c>
+      <c r="K326" s="11">
+        <v>0</v>
+      </c>
+      <c r="L326" s="11">
+        <v>1</v>
+      </c>
+      <c r="M326" s="11">
+        <v>0</v>
+      </c>
+      <c r="N326" s="11">
+        <v>9</v>
+      </c>
+      <c r="O326" s="11">
+        <v>5</v>
+      </c>
+      <c r="P326" s="11">
+        <v>7</v>
+      </c>
+      <c r="Q326" s="11">
+        <v>3</v>
+      </c>
+      <c r="R326" s="11">
+        <v>2</v>
+      </c>
+      <c r="S326" s="11">
+        <v>0</v>
+      </c>
+      <c r="T326" s="11">
+        <v>120</v>
+      </c>
+      <c r="U326" s="11">
+        <v>246</v>
+      </c>
+      <c r="W326" s="11">
+        <v>0</v>
+      </c>
+      <c r="X326" s="11">
+        <v>43</v>
+      </c>
+      <c r="Y326" s="11">
+        <v>8</v>
+      </c>
+      <c r="Z326" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="AA326" s="11">
+        <v>32</v>
       </c>
       <c r="AB326" s="1">
         <v>21.5</v>
@@ -39267,7 +39042,7 @@
     </row>
     <row r="331" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A331" s="4" t="s">
-        <v>630</v>
+        <v>554</v>
       </c>
       <c r="B331" s="1" t="s">
         <v>32</v>
@@ -39363,7 +39138,7 @@
     </row>
     <row r="332" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A332" s="1" t="s">
-        <v>351</v>
+        <v>275</v>
       </c>
       <c r="B332" s="1" t="s">
         <v>32</v>
@@ -39839,7 +39614,7 @@
     </row>
     <row r="337" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A337" s="1" t="s">
-        <v>369</v>
+        <v>293</v>
       </c>
       <c r="B337" s="1" t="s">
         <v>32</v>
@@ -39934,7 +39709,7 @@
     </row>
     <row r="338" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A338" s="1" t="s">
-        <v>381</v>
+        <v>305</v>
       </c>
       <c r="B338" s="1" t="s">
         <v>32</v>
@@ -40505,7 +40280,7 @@
     </row>
     <row r="344" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A344" s="4" t="s">
-        <v>623</v>
+        <v>547</v>
       </c>
       <c r="B344" s="1" t="s">
         <v>32</v>
@@ -40601,7 +40376,7 @@
     </row>
     <row r="345" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A345" s="1" t="s">
-        <v>394</v>
+        <v>318</v>
       </c>
       <c r="B345" s="1" t="s">
         <v>32</v>
@@ -40887,7 +40662,7 @@
     </row>
     <row r="348" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A348" s="4" t="s">
-        <v>628</v>
+        <v>552</v>
       </c>
       <c r="B348" s="1" t="s">
         <v>32</v>
@@ -41078,7 +40853,7 @@
     </row>
     <row r="350" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A350" s="1" t="s">
-        <v>407</v>
+        <v>331</v>
       </c>
       <c r="B350" s="1" t="s">
         <v>32</v>
@@ -41173,7 +40948,7 @@
     </row>
     <row r="351" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A351" s="1" t="s">
-        <v>411</v>
+        <v>335</v>
       </c>
       <c r="B351" s="1" t="s">
         <v>32</v>
@@ -41364,7 +41139,7 @@
     </row>
     <row r="353" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A353" s="4" t="s">
-        <v>637</v>
+        <v>561</v>
       </c>
       <c r="B353" s="1" t="s">
         <v>32</v>
@@ -41556,7 +41331,7 @@
     </row>
     <row r="355" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" s="4" t="s">
-        <v>640</v>
+        <v>564</v>
       </c>
       <c r="B355" s="1" t="s">
         <v>32</v>
@@ -41652,7 +41427,7 @@
     </row>
     <row r="356" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A356" s="4" t="s">
-        <v>475</v>
+        <v>399</v>
       </c>
       <c r="B356" s="1" t="s">
         <v>32</v>
@@ -41748,7 +41523,7 @@
     </row>
     <row r="357" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A357" s="4" t="s">
-        <v>650</v>
+        <v>574</v>
       </c>
       <c r="B357" s="1" t="s">
         <v>32</v>
@@ -41844,7 +41619,7 @@
     </row>
     <row r="358" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A358" s="1" t="s">
-        <v>431</v>
+        <v>355</v>
       </c>
       <c r="B358" s="1" t="s">
         <v>32</v>
@@ -41939,7 +41714,7 @@
     </row>
     <row r="359" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A359" s="1" t="s">
-        <v>535</v>
+        <v>459</v>
       </c>
       <c r="B359" s="1" t="s">
         <v>32</v>
@@ -42034,7 +41809,7 @@
     </row>
     <row r="360" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A360" s="1" t="s">
-        <v>548</v>
+        <v>472</v>
       </c>
       <c r="B360" s="1" t="s">
         <v>32</v>
@@ -42129,7 +41904,7 @@
     </row>
     <row r="361" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A361" s="1" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B361" s="1" t="s">
         <v>32</v>
@@ -42137,74 +41912,74 @@
       <c r="C361" s="1">
         <v>1</v>
       </c>
-      <c r="D361" s="1" t="s">
-        <v>192</v>
+      <c r="D361" s="11">
+        <v>600</v>
       </c>
       <c r="E361" s="5">
         <v>1</v>
       </c>
-      <c r="F361" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="G361" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="H361" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="I361" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="J361" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="K361" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="L361" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="M361" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="N361" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="O361" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="P361" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="Q361" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="R361" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="S361" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="T361" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="U361" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="W361" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="X361" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="Y361" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="Z361" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="AA361" s="1" t="s">
-        <v>198</v>
+      <c r="F361" s="11">
+        <v>600</v>
+      </c>
+      <c r="G361" s="11">
+        <v>0</v>
+      </c>
+      <c r="H361" s="11">
+        <v>8</v>
+      </c>
+      <c r="I361" s="11">
+        <v>0</v>
+      </c>
+      <c r="J361" s="11">
+        <v>2</v>
+      </c>
+      <c r="K361" s="11">
+        <v>0</v>
+      </c>
+      <c r="L361" s="11">
+        <v>1</v>
+      </c>
+      <c r="M361" s="11">
+        <v>0</v>
+      </c>
+      <c r="N361" s="11">
+        <v>5</v>
+      </c>
+      <c r="O361" s="11">
+        <v>0</v>
+      </c>
+      <c r="P361" s="11">
+        <v>8</v>
+      </c>
+      <c r="Q361" s="11">
+        <v>3</v>
+      </c>
+      <c r="R361" s="11">
+        <v>0</v>
+      </c>
+      <c r="S361" s="11">
+        <v>0</v>
+      </c>
+      <c r="T361" s="11">
+        <v>105</v>
+      </c>
+      <c r="U361" s="11">
+        <v>212</v>
+      </c>
+      <c r="W361" s="11">
+        <v>0</v>
+      </c>
+      <c r="X361" s="11">
+        <v>0</v>
+      </c>
+      <c r="Y361" s="11">
+        <v>8</v>
+      </c>
+      <c r="Z361" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="AA361" s="11">
+        <v>30</v>
       </c>
       <c r="AB361" s="1">
         <v>19</v>
@@ -42320,7 +42095,7 @@
     </row>
     <row r="363" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A363" s="1" t="s">
-        <v>320</v>
+        <v>244</v>
       </c>
       <c r="B363" s="1" t="s">
         <v>32</v>
@@ -42415,7 +42190,7 @@
     </row>
     <row r="364" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A364" s="1" t="s">
-        <v>325</v>
+        <v>249</v>
       </c>
       <c r="B364" s="1" t="s">
         <v>32</v>
@@ -42605,7 +42380,7 @@
     </row>
     <row r="366" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A366" s="1" t="s">
-        <v>495</v>
+        <v>419</v>
       </c>
       <c r="B366" s="1" t="s">
         <v>32</v>
@@ -42704,7 +42479,7 @@
     </row>
     <row r="367" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A367" s="1" t="s">
-        <v>500</v>
+        <v>424</v>
       </c>
       <c r="B367" s="1" t="s">
         <v>32</v>
@@ -42898,7 +42673,7 @@
     </row>
     <row r="369" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A369" s="1" t="s">
-        <v>517</v>
+        <v>441</v>
       </c>
       <c r="B369" s="1" t="s">
         <v>32</v>
@@ -42993,7 +42768,7 @@
     </row>
     <row r="370" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A370" s="1" t="s">
-        <v>379</v>
+        <v>303</v>
       </c>
       <c r="B370" s="1" t="s">
         <v>76</v>
@@ -43183,7 +42958,7 @@
     </row>
     <row r="372" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A372" s="1" t="s">
-        <v>385</v>
+        <v>309</v>
       </c>
       <c r="B372" s="1" t="s">
         <v>32</v>
@@ -43278,7 +43053,7 @@
     </row>
     <row r="373" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A373" s="1" t="s">
-        <v>212</v>
+        <v>189</v>
       </c>
       <c r="B373" s="1" t="s">
         <v>32</v>
@@ -43286,74 +43061,74 @@
       <c r="C373" s="1">
         <v>1</v>
       </c>
-      <c r="D373" s="1" t="s">
-        <v>213</v>
+      <c r="D373" s="11">
+        <v>800</v>
       </c>
       <c r="E373" s="5">
         <v>1</v>
       </c>
-      <c r="F373" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="G373" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="H373" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="I373" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="J373" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="K373" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="L373" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="M373" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="N373" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="O373" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="P373" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="Q373" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="R373" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="S373" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="T373" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="U373" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="W373" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="X373" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="Y373" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="Z373" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="AA373" s="1" t="s">
-        <v>198</v>
+      <c r="F373" s="11">
+        <v>800</v>
+      </c>
+      <c r="G373" s="11">
+        <v>0</v>
+      </c>
+      <c r="H373" s="11">
+        <v>8</v>
+      </c>
+      <c r="I373" s="11">
+        <v>0</v>
+      </c>
+      <c r="J373" s="11">
+        <v>2</v>
+      </c>
+      <c r="K373" s="11">
+        <v>0</v>
+      </c>
+      <c r="L373" s="11">
+        <v>1</v>
+      </c>
+      <c r="M373" s="11">
+        <v>0</v>
+      </c>
+      <c r="N373" s="11">
+        <v>6</v>
+      </c>
+      <c r="O373" s="11">
+        <v>0</v>
+      </c>
+      <c r="P373" s="11">
+        <v>7</v>
+      </c>
+      <c r="Q373" s="11">
+        <v>4</v>
+      </c>
+      <c r="R373" s="11">
+        <v>0</v>
+      </c>
+      <c r="S373" s="11">
+        <v>0</v>
+      </c>
+      <c r="T373" s="11">
+        <v>120</v>
+      </c>
+      <c r="U373" s="11">
+        <v>244</v>
+      </c>
+      <c r="W373" s="11">
+        <v>0</v>
+      </c>
+      <c r="X373" s="11">
+        <v>0</v>
+      </c>
+      <c r="Y373" s="11">
+        <v>8</v>
+      </c>
+      <c r="Z373" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="AA373" s="11">
+        <v>30</v>
       </c>
       <c r="AB373" s="1">
         <v>21.5</v>
@@ -43374,7 +43149,7 @@
     </row>
     <row r="374" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A374" s="1" t="s">
-        <v>228</v>
+        <v>193</v>
       </c>
       <c r="B374" s="1" t="s">
         <v>32</v>
@@ -43473,7 +43248,7 @@
     </row>
     <row r="375" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A375" s="1" t="s">
-        <v>229</v>
+        <v>194</v>
       </c>
       <c r="B375" s="1" t="s">
         <v>32</v>
@@ -43572,7 +43347,7 @@
     </row>
     <row r="376" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A376" s="4" t="s">
-        <v>558</v>
+        <v>482</v>
       </c>
       <c r="B376" s="4" t="s">
         <v>32</v>
@@ -43668,7 +43443,7 @@
     </row>
     <row r="377" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A377" s="1" t="s">
-        <v>567</v>
+        <v>491</v>
       </c>
       <c r="B377" s="1" t="s">
         <v>32</v>
@@ -43763,7 +43538,7 @@
     </row>
     <row r="378" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A378" s="1" t="s">
-        <v>509</v>
+        <v>433</v>
       </c>
       <c r="B378" s="1" t="s">
         <v>32</v>
@@ -43862,7 +43637,7 @@
     </row>
     <row r="379" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A379" s="1" t="s">
-        <v>510</v>
+        <v>434</v>
       </c>
       <c r="B379" s="1" t="s">
         <v>32</v>
@@ -43961,7 +43736,7 @@
     </row>
     <row r="380" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A380" s="1" t="s">
-        <v>577</v>
+        <v>501</v>
       </c>
       <c r="B380" s="1" t="s">
         <v>32</v>
@@ -44056,7 +43831,7 @@
     </row>
     <row r="381" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A381" s="1" t="s">
-        <v>578</v>
+        <v>502</v>
       </c>
       <c r="B381" s="1" t="s">
         <v>32</v>
@@ -44151,7 +43926,7 @@
     </row>
     <row r="382" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A382" s="1" t="s">
-        <v>331</v>
+        <v>255</v>
       </c>
       <c r="B382" s="1" t="s">
         <v>32</v>
@@ -44341,7 +44116,7 @@
     </row>
     <row r="384" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A384" s="1" t="s">
-        <v>591</v>
+        <v>515</v>
       </c>
       <c r="B384" s="1" t="s">
         <v>32</v>
@@ -44436,7 +44211,7 @@
     </row>
     <row r="385" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A385" s="1" t="s">
-        <v>266</v>
+        <v>202</v>
       </c>
       <c r="B385" s="1" t="s">
         <v>32</v>
@@ -44444,74 +44219,74 @@
       <c r="C385" s="1">
         <v>1</v>
       </c>
-      <c r="D385" s="1" t="s">
-        <v>267</v>
+      <c r="D385" s="11">
+        <v>1250</v>
       </c>
       <c r="E385" s="5">
         <v>1</v>
       </c>
-      <c r="F385" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="G385" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="H385" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="I385" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="J385" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="K385" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="L385" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="M385" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="N385" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="O385" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="P385" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="Q385" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="R385" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="S385" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="T385" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="U385" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="W385" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="X385" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="Y385" s="1" t="s">
-        <v>203</v>
+      <c r="F385" s="11">
+        <v>1250</v>
+      </c>
+      <c r="G385" s="11">
+        <v>0</v>
+      </c>
+      <c r="H385" s="11">
+        <v>9</v>
+      </c>
+      <c r="I385" s="11">
+        <v>0</v>
+      </c>
+      <c r="J385" s="11">
+        <v>3</v>
+      </c>
+      <c r="K385" s="11">
+        <v>0</v>
+      </c>
+      <c r="L385" s="11">
+        <v>2</v>
+      </c>
+      <c r="M385" s="11">
+        <v>0</v>
+      </c>
+      <c r="N385" s="11">
+        <v>16</v>
+      </c>
+      <c r="O385" s="11">
+        <v>0</v>
+      </c>
+      <c r="P385" s="11">
+        <v>11</v>
+      </c>
+      <c r="Q385" s="11">
+        <v>4</v>
+      </c>
+      <c r="R385" s="11">
+        <v>0</v>
+      </c>
+      <c r="S385" s="11">
+        <v>0</v>
+      </c>
+      <c r="T385" s="11">
+        <v>222</v>
+      </c>
+      <c r="U385" s="11">
+        <v>460</v>
+      </c>
+      <c r="W385" s="11">
+        <v>0</v>
+      </c>
+      <c r="X385" s="11">
+        <v>0</v>
+      </c>
+      <c r="Y385" s="11">
+        <v>9</v>
       </c>
       <c r="Z385" s="1">
         <v>0.83299999999999996</v>
       </c>
-      <c r="AA385" s="1" t="s">
-        <v>270</v>
+      <c r="AA385" s="11">
+        <v>64</v>
       </c>
       <c r="AB385" s="1">
         <v>23.6</v>
@@ -44532,7 +44307,7 @@
     </row>
     <row r="386" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A386" s="1" t="s">
-        <v>321</v>
+        <v>245</v>
       </c>
       <c r="B386" s="1" t="s">
         <v>32</v>
@@ -44722,7 +44497,7 @@
     </row>
     <row r="388" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A388" s="1" t="s">
-        <v>428</v>
+        <v>352</v>
       </c>
       <c r="B388" s="1" t="s">
         <v>32</v>
@@ -44817,7 +44592,7 @@
     </row>
     <row r="389" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A389" s="4" t="s">
-        <v>476</v>
+        <v>400</v>
       </c>
       <c r="B389" s="1" t="s">
         <v>32</v>
@@ -44913,7 +44688,7 @@
     </row>
     <row r="390" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A390" s="4" t="s">
-        <v>651</v>
+        <v>575</v>
       </c>
       <c r="B390" s="1" t="s">
         <v>32</v>
@@ -45009,7 +44784,7 @@
     </row>
     <row r="391" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A391" s="1" t="s">
-        <v>438</v>
+        <v>362</v>
       </c>
       <c r="B391" s="1" t="s">
         <v>32</v>
@@ -45104,7 +44879,7 @@
     </row>
     <row r="392" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A392" s="1" t="s">
-        <v>595</v>
+        <v>519</v>
       </c>
       <c r="B392" s="1" t="s">
         <v>32</v>
@@ -45199,7 +44974,7 @@
     </row>
     <row r="393" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A393" s="1" t="s">
-        <v>562</v>
+        <v>486</v>
       </c>
       <c r="B393" s="1" t="s">
         <v>32</v>
@@ -45294,7 +45069,7 @@
     </row>
     <row r="394" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A394" s="1" t="s">
-        <v>365</v>
+        <v>289</v>
       </c>
       <c r="B394" s="1" t="s">
         <v>32</v>
@@ -45389,7 +45164,7 @@
     </row>
     <row r="395" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A395" s="1" t="s">
-        <v>576</v>
+        <v>500</v>
       </c>
       <c r="B395" s="1" t="s">
         <v>32</v>
@@ -45484,7 +45259,7 @@
     </row>
     <row r="396" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A396" s="1" t="s">
-        <v>299</v>
+        <v>223</v>
       </c>
       <c r="B396" s="1" t="s">
         <v>32</v>
@@ -45581,7 +45356,7 @@
     </row>
     <row r="397" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A397" s="1" t="s">
-        <v>367</v>
+        <v>291</v>
       </c>
       <c r="B397" s="1" t="s">
         <v>32</v>
@@ -45771,7 +45546,7 @@
     </row>
     <row r="399" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A399" s="1" t="s">
-        <v>426</v>
+        <v>350</v>
       </c>
       <c r="B399" s="1" t="s">
         <v>32</v>
@@ -45866,7 +45641,7 @@
     </row>
     <row r="400" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A400" s="1" t="s">
-        <v>496</v>
+        <v>420</v>
       </c>
       <c r="B400" s="1" t="s">
         <v>32</v>
@@ -45965,7 +45740,7 @@
     </row>
     <row r="401" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A401" s="1" t="s">
-        <v>305</v>
+        <v>229</v>
       </c>
       <c r="B401" s="1" t="s">
         <v>32</v>
@@ -46063,7 +45838,7 @@
     </row>
     <row r="402" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A402" s="1" t="s">
-        <v>376</v>
+        <v>300</v>
       </c>
       <c r="B402" s="1" t="s">
         <v>32</v>
@@ -46158,7 +45933,7 @@
     </row>
     <row r="403" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A403" s="1" t="s">
-        <v>306</v>
+        <v>230</v>
       </c>
       <c r="B403" s="1" t="s">
         <v>32</v>
@@ -46351,7 +46126,7 @@
     </row>
     <row r="405" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A405" s="4" t="s">
-        <v>614</v>
+        <v>538</v>
       </c>
       <c r="B405" s="1" t="s">
         <v>32</v>
@@ -46543,7 +46318,7 @@
     </row>
     <row r="407" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A407" s="4" t="s">
-        <v>607</v>
+        <v>531</v>
       </c>
       <c r="B407" s="1" t="s">
         <v>32</v>
@@ -46734,7 +46509,7 @@
     </row>
     <row r="409" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A409" s="1" t="s">
-        <v>534</v>
+        <v>458</v>
       </c>
       <c r="B409" s="1" t="s">
         <v>32</v>
@@ -46924,7 +46699,7 @@
     </row>
     <row r="411" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A411" s="1" t="s">
-        <v>359</v>
+        <v>283</v>
       </c>
       <c r="B411" s="1" t="s">
         <v>32</v>
@@ -47019,7 +46794,7 @@
     </row>
     <row r="412" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A412" s="1" t="s">
-        <v>399</v>
+        <v>323</v>
       </c>
       <c r="B412" s="1" t="s">
         <v>32</v>
@@ -47114,7 +46889,7 @@
     </row>
     <row r="413" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A413" s="1" t="s">
-        <v>554</v>
+        <v>478</v>
       </c>
       <c r="B413" s="1" t="s">
         <v>32</v>
@@ -47210,7 +46985,7 @@
     </row>
     <row r="414" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A414" s="1" t="s">
-        <v>555</v>
+        <v>479</v>
       </c>
       <c r="B414" s="1" t="s">
         <v>32</v>
@@ -47306,7 +47081,7 @@
     </row>
     <row r="415" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A415" s="1" t="s">
-        <v>458</v>
+        <v>382</v>
       </c>
       <c r="B415" s="1" t="s">
         <v>32</v>
@@ -47402,7 +47177,7 @@
     </row>
     <row r="416" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A416" s="1" t="s">
-        <v>459</v>
+        <v>383</v>
       </c>
       <c r="B416" s="1" t="s">
         <v>32</v>
@@ -47499,7 +47274,7 @@
     </row>
     <row r="417" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A417" s="1" t="s">
-        <v>550</v>
+        <v>474</v>
       </c>
       <c r="B417" s="1" t="s">
         <v>32</v>
@@ -47595,7 +47370,7 @@
     </row>
     <row r="418" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A418" s="1" t="s">
-        <v>551</v>
+        <v>475</v>
       </c>
       <c r="B418" s="1" t="s">
         <v>32</v>
@@ -47691,7 +47466,7 @@
     </row>
     <row r="419" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A419" s="1" t="s">
-        <v>460</v>
+        <v>384</v>
       </c>
       <c r="B419" s="1" t="s">
         <v>32</v>
@@ -47787,7 +47562,7 @@
     </row>
     <row r="420" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A420" s="1" t="s">
-        <v>461</v>
+        <v>385</v>
       </c>
       <c r="B420" s="1" t="s">
         <v>32</v>
@@ -47884,7 +47659,7 @@
     </row>
     <row r="421" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A421" s="1" t="s">
-        <v>501</v>
+        <v>425</v>
       </c>
       <c r="B421" s="1" t="s">
         <v>32</v>
@@ -48079,7 +47854,7 @@
     </row>
     <row r="423" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A423" s="4" t="s">
-        <v>635</v>
+        <v>559</v>
       </c>
       <c r="B423" s="1" t="s">
         <v>32</v>
@@ -48175,7 +47950,7 @@
     </row>
     <row r="424" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A424" s="1" t="s">
-        <v>285</v>
+        <v>211</v>
       </c>
       <c r="B424" s="1" t="s">
         <v>32</v>
@@ -48183,8 +47958,8 @@
       <c r="C424" s="1">
         <v>1</v>
       </c>
-      <c r="D424" s="1" t="s">
-        <v>286</v>
+      <c r="D424" s="11">
+        <v>1381</v>
       </c>
       <c r="E424" s="5">
         <v>1</v>
@@ -48272,7 +48047,7 @@
     </row>
     <row r="425" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A425" s="1" t="s">
-        <v>424</v>
+        <v>348</v>
       </c>
       <c r="B425" s="1" t="s">
         <v>32</v>
@@ -48367,7 +48142,7 @@
     </row>
     <row r="426" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A426" s="1" t="s">
-        <v>456</v>
+        <v>380</v>
       </c>
       <c r="B426" s="1" t="s">
         <v>32</v>
@@ -48463,7 +48238,7 @@
     </row>
     <row r="427" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A427" s="1" t="s">
-        <v>457</v>
+        <v>381</v>
       </c>
       <c r="B427" s="1" t="s">
         <v>32</v>
@@ -48655,7 +48430,7 @@
     </row>
     <row r="429" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A429" s="1" t="s">
-        <v>514</v>
+        <v>438</v>
       </c>
       <c r="B429" s="1" t="s">
         <v>32</v>
@@ -48845,7 +48620,7 @@
     </row>
     <row r="431" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A431" s="1" t="s">
-        <v>666</v>
+        <v>590</v>
       </c>
       <c r="B431" s="1" t="s">
         <v>32</v>
@@ -49036,7 +48811,7 @@
     </row>
     <row r="433" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A433" s="4" t="s">
-        <v>620</v>
+        <v>544</v>
       </c>
       <c r="B433" s="1" t="s">
         <v>32</v>
@@ -49227,7 +49002,7 @@
     </row>
     <row r="435" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A435" s="1" t="s">
-        <v>502</v>
+        <v>426</v>
       </c>
       <c r="B435" s="1" t="s">
         <v>32</v>
@@ -49326,7 +49101,7 @@
     </row>
     <row r="436" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A436" s="1" t="s">
-        <v>465</v>
+        <v>389</v>
       </c>
       <c r="B436" s="1" t="s">
         <v>32</v>
@@ -49421,7 +49196,7 @@
     </row>
     <row r="437" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A437" s="1" t="s">
-        <v>432</v>
+        <v>356</v>
       </c>
       <c r="B437" s="1" t="s">
         <v>32</v>
@@ -49612,7 +49387,7 @@
     </row>
     <row r="439" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A439" s="4" t="s">
-        <v>610</v>
+        <v>534</v>
       </c>
       <c r="B439" s="1" t="s">
         <v>32</v>
@@ -49803,7 +49578,7 @@
     </row>
     <row r="441" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A441" s="1" t="s">
-        <v>664</v>
+        <v>588</v>
       </c>
       <c r="B441" s="1" t="s">
         <v>32</v>
@@ -49898,7 +49673,7 @@
     </row>
     <row r="442" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A442" s="1" t="s">
-        <v>472</v>
+        <v>396</v>
       </c>
       <c r="B442" s="1" t="s">
         <v>32</v>
@@ -49993,7 +49768,7 @@
     </row>
     <row r="443" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A443" s="4" t="s">
-        <v>481</v>
+        <v>405</v>
       </c>
       <c r="B443" s="1" t="s">
         <v>32</v>
@@ -50089,7 +49864,7 @@
     </row>
     <row r="444" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A444" s="4" t="s">
-        <v>655</v>
+        <v>579</v>
       </c>
       <c r="B444" s="1" t="s">
         <v>32</v>
@@ -50185,7 +49960,7 @@
     </row>
     <row r="445" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A445" s="1" t="s">
-        <v>296</v>
+        <v>220</v>
       </c>
       <c r="B445" s="1" t="s">
         <v>32</v>
@@ -50282,7 +50057,7 @@
     </row>
     <row r="446" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A446" s="1" t="s">
-        <v>301</v>
+        <v>225</v>
       </c>
       <c r="B446" s="1" t="s">
         <v>32</v>
@@ -50380,7 +50155,7 @@
     </row>
     <row r="447" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A447" s="1" t="s">
-        <v>522</v>
+        <v>446</v>
       </c>
       <c r="B447" s="1" t="s">
         <v>32</v>
@@ -50475,7 +50250,7 @@
     </row>
     <row r="448" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A448" s="1" t="s">
-        <v>370</v>
+        <v>294</v>
       </c>
       <c r="B448" s="1" t="s">
         <v>32</v>
@@ -50666,7 +50441,7 @@
     </row>
     <row r="450" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A450" s="4" t="s">
-        <v>641</v>
+        <v>565</v>
       </c>
       <c r="B450" s="1" t="s">
         <v>32</v>
@@ -50762,7 +50537,7 @@
     </row>
     <row r="451" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A451" s="1" t="s">
-        <v>525</v>
+        <v>449</v>
       </c>
       <c r="B451" s="1" t="s">
         <v>32</v>
@@ -50857,7 +50632,7 @@
     </row>
     <row r="452" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A452" s="1" t="s">
-        <v>532</v>
+        <v>456</v>
       </c>
       <c r="B452" s="1" t="s">
         <v>32</v>
@@ -50952,7 +50727,7 @@
     </row>
     <row r="453" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A453" s="1" t="s">
-        <v>542</v>
+        <v>466</v>
       </c>
       <c r="B453" s="1" t="s">
         <v>32</v>
@@ -51047,7 +50822,7 @@
     </row>
     <row r="454" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A454" s="1" t="s">
-        <v>439</v>
+        <v>363</v>
       </c>
       <c r="B454" s="1" t="s">
         <v>32</v>
@@ -51142,7 +50917,7 @@
     </row>
     <row r="455" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A455" s="1" t="s">
-        <v>304</v>
+        <v>228</v>
       </c>
       <c r="B455" s="1" t="s">
         <v>32</v>
@@ -51240,7 +51015,7 @@
     </row>
     <row r="456" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A456" s="1" t="s">
-        <v>487</v>
+        <v>411</v>
       </c>
       <c r="B456" s="1" t="s">
         <v>32</v>
@@ -51430,7 +51205,7 @@
     </row>
     <row r="458" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A458" s="1" t="s">
-        <v>309</v>
+        <v>233</v>
       </c>
       <c r="B458" s="1" t="s">
         <v>32</v>
@@ -51526,7 +51301,7 @@
     </row>
     <row r="459" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A459" s="1" t="s">
-        <v>388</v>
+        <v>312</v>
       </c>
       <c r="B459" s="1" t="s">
         <v>32</v>
@@ -51621,7 +51396,7 @@
     </row>
     <row r="460" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A460" s="1" t="s">
-        <v>386</v>
+        <v>310</v>
       </c>
       <c r="B460" s="1" t="s">
         <v>32</v>
@@ -51716,7 +51491,7 @@
     </row>
     <row r="461" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A461" s="1" t="s">
-        <v>401</v>
+        <v>325</v>
       </c>
       <c r="B461" s="1" t="s">
         <v>32</v>
@@ -51811,7 +51586,7 @@
     </row>
     <row r="462" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A462" s="1" t="s">
-        <v>298</v>
+        <v>222</v>
       </c>
       <c r="B462" s="1" t="s">
         <v>32</v>
@@ -51908,7 +51683,7 @@
     </row>
     <row r="463" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A463" s="1" t="s">
-        <v>300</v>
+        <v>224</v>
       </c>
       <c r="B463" s="1" t="s">
         <v>32</v>
@@ -52101,7 +51876,7 @@
     </row>
     <row r="465" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A465" s="4" t="s">
-        <v>482</v>
+        <v>406</v>
       </c>
       <c r="B465" s="1" t="s">
         <v>32</v>
@@ -52197,7 +51972,7 @@
     </row>
     <row r="466" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A466" s="4" t="s">
-        <v>656</v>
+        <v>580</v>
       </c>
       <c r="B466" s="1" t="s">
         <v>32</v>
@@ -52293,7 +52068,7 @@
     </row>
     <row r="467" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A467" s="1" t="s">
-        <v>434</v>
+        <v>358</v>
       </c>
       <c r="B467" s="1" t="s">
         <v>32</v>
@@ -52388,7 +52163,7 @@
     </row>
     <row r="468" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A468" s="1" t="s">
-        <v>311</v>
+        <v>235</v>
       </c>
       <c r="B468" s="1" t="s">
         <v>32</v>
@@ -52485,7 +52260,7 @@
     </row>
     <row r="469" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A469" s="4" t="s">
-        <v>480</v>
+        <v>404</v>
       </c>
       <c r="B469" s="1" t="s">
         <v>32</v>
@@ -52581,7 +52356,7 @@
     </row>
     <row r="470" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A470" s="4" t="s">
-        <v>654</v>
+        <v>578</v>
       </c>
       <c r="B470" s="1" t="s">
         <v>32</v>
@@ -52773,7 +52548,7 @@
     </row>
     <row r="472" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A472" s="4" t="s">
-        <v>631</v>
+        <v>555</v>
       </c>
       <c r="B472" s="1" t="s">
         <v>32</v>
@@ -52869,7 +52644,7 @@
     </row>
     <row r="473" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A473" s="1" t="s">
-        <v>569</v>
+        <v>493</v>
       </c>
       <c r="B473" s="1" t="s">
         <v>32</v>
@@ -53059,7 +52834,7 @@
     </row>
     <row r="475" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A475" s="1" t="s">
-        <v>544</v>
+        <v>468</v>
       </c>
       <c r="B475" s="1" t="s">
         <v>32</v>
@@ -53154,7 +52929,7 @@
     </row>
     <row r="476" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A476" s="1" t="s">
-        <v>416</v>
+        <v>340</v>
       </c>
       <c r="B476" s="1" t="s">
         <v>32</v>
@@ -53249,7 +53024,7 @@
     </row>
     <row r="477" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A477" s="1" t="s">
-        <v>297</v>
+        <v>221</v>
       </c>
       <c r="B477" s="1" t="s">
         <v>32</v>
@@ -53346,7 +53121,7 @@
     </row>
     <row r="478" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A478" s="4" t="s">
-        <v>485</v>
+        <v>409</v>
       </c>
       <c r="B478" s="1" t="s">
         <v>32</v>
@@ -53442,7 +53217,7 @@
     </row>
     <row r="479" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A479" s="4" t="s">
-        <v>659</v>
+        <v>583</v>
       </c>
       <c r="B479" s="1" t="s">
         <v>32</v>
@@ -53538,7 +53313,7 @@
     </row>
     <row r="480" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A480" s="4" t="s">
-        <v>478</v>
+        <v>402</v>
       </c>
       <c r="B480" s="1" t="s">
         <v>32</v>
@@ -53634,7 +53409,7 @@
     </row>
     <row r="481" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A481" s="4" t="s">
-        <v>652</v>
+        <v>576</v>
       </c>
       <c r="B481" s="1" t="s">
         <v>32</v>
@@ -53730,7 +53505,7 @@
     </row>
     <row r="482" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A482" s="1" t="s">
-        <v>390</v>
+        <v>314</v>
       </c>
       <c r="B482" s="1" t="s">
         <v>32</v>
@@ -53825,7 +53600,7 @@
     </row>
     <row r="483" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A483" s="4" t="s">
-        <v>468</v>
+        <v>392</v>
       </c>
       <c r="B483" s="1" t="s">
         <v>32</v>
@@ -53921,7 +53696,7 @@
     </row>
     <row r="484" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A484" s="4" t="s">
-        <v>645</v>
+        <v>569</v>
       </c>
       <c r="B484" s="1" t="s">
         <v>32</v>
@@ -54017,7 +53792,7 @@
     </row>
     <row r="485" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A485" s="1" t="s">
-        <v>436</v>
+        <v>360</v>
       </c>
       <c r="B485" s="1" t="s">
         <v>32</v>
@@ -54112,7 +53887,7 @@
     </row>
     <row r="486" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A486" s="4" t="s">
-        <v>479</v>
+        <v>403</v>
       </c>
       <c r="B486" s="1" t="s">
         <v>32</v>
@@ -54208,7 +53983,7 @@
     </row>
     <row r="487" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A487" s="4" t="s">
-        <v>653</v>
+        <v>577</v>
       </c>
       <c r="B487" s="1" t="s">
         <v>32</v>
@@ -54304,7 +54079,7 @@
     </row>
     <row r="488" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A488" s="1" t="s">
-        <v>512</v>
+        <v>436</v>
       </c>
       <c r="B488" s="1" t="s">
         <v>32</v>
@@ -54399,7 +54174,7 @@
     </row>
     <row r="489" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A489" s="1" t="s">
-        <v>393</v>
+        <v>317</v>
       </c>
       <c r="B489" s="1" t="s">
         <v>32</v>
@@ -54494,7 +54269,7 @@
     </row>
     <row r="490" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A490" s="1" t="s">
-        <v>524</v>
+        <v>448</v>
       </c>
       <c r="B490" s="1" t="s">
         <v>32</v>
@@ -54779,7 +54554,7 @@
     </row>
     <row r="493" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A493" s="1" t="s">
-        <v>450</v>
+        <v>374</v>
       </c>
       <c r="B493" s="1" t="s">
         <v>32</v>
@@ -54879,7 +54654,7 @@
     </row>
     <row r="494" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A494" s="1" t="s">
-        <v>427</v>
+        <v>351</v>
       </c>
       <c r="B494" s="1" t="s">
         <v>32</v>
@@ -54974,7 +54749,7 @@
     </row>
     <row r="495" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A495" s="1" t="s">
-        <v>293</v>
+        <v>217</v>
       </c>
       <c r="B495" s="1" t="s">
         <v>32</v>
@@ -55070,7 +54845,7 @@
     </row>
     <row r="496" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A496" s="1" t="s">
-        <v>592</v>
+        <v>516</v>
       </c>
       <c r="B496" s="1" t="s">
         <v>32</v>
@@ -55165,7 +54940,7 @@
     </row>
     <row r="497" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A497" s="1" t="s">
-        <v>552</v>
+        <v>476</v>
       </c>
       <c r="B497" s="1" t="s">
         <v>32</v>
@@ -55260,7 +55035,7 @@
     </row>
     <row r="498" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A498" s="1" t="s">
-        <v>553</v>
+        <v>477</v>
       </c>
       <c r="B498" s="1" t="s">
         <v>32</v>
@@ -55355,7 +55130,7 @@
     </row>
     <row r="499" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A499" s="1" t="s">
-        <v>294</v>
+        <v>218</v>
       </c>
       <c r="B499" s="1" t="s">
         <v>32</v>
@@ -55547,7 +55322,7 @@
     </row>
     <row r="501" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A501" s="1" t="s">
-        <v>262</v>
+        <v>201</v>
       </c>
       <c r="B501" s="1" t="s">
         <v>32</v>
@@ -55555,74 +55330,74 @@
       <c r="C501" s="1">
         <v>1</v>
       </c>
-      <c r="D501" s="1" t="s">
-        <v>263</v>
+      <c r="D501" s="11">
+        <v>1232</v>
       </c>
       <c r="E501" s="5">
         <v>1</v>
       </c>
-      <c r="F501" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="G501" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="H501" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="I501" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="J501" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="K501" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="L501" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="M501" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="N501" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="O501" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="P501" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="Q501" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="R501" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="S501" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="T501" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="U501" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="W501" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="X501" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="Y501" s="1" t="s">
-        <v>193</v>
+      <c r="F501" s="11">
+        <v>1232</v>
+      </c>
+      <c r="G501" s="11">
+        <v>0</v>
+      </c>
+      <c r="H501" s="11">
+        <v>8</v>
+      </c>
+      <c r="I501" s="11">
+        <v>0</v>
+      </c>
+      <c r="J501" s="11">
+        <v>3</v>
+      </c>
+      <c r="K501" s="11">
+        <v>0</v>
+      </c>
+      <c r="L501" s="11">
+        <v>2</v>
+      </c>
+      <c r="M501" s="11">
+        <v>0</v>
+      </c>
+      <c r="N501" s="11">
+        <v>10</v>
+      </c>
+      <c r="O501" s="11">
+        <v>0</v>
+      </c>
+      <c r="P501" s="11">
+        <v>13</v>
+      </c>
+      <c r="Q501" s="11">
+        <v>3</v>
+      </c>
+      <c r="R501" s="11">
+        <v>0</v>
+      </c>
+      <c r="S501" s="11">
+        <v>0</v>
+      </c>
+      <c r="T501" s="11">
+        <v>200</v>
+      </c>
+      <c r="U501" s="11">
+        <v>420</v>
+      </c>
+      <c r="W501" s="11">
+        <v>0</v>
+      </c>
+      <c r="X501" s="11">
+        <v>0</v>
+      </c>
+      <c r="Y501" s="11">
+        <v>8</v>
       </c>
       <c r="Z501" s="1">
         <v>0.58299999999999996</v>
       </c>
-      <c r="AA501" s="1" t="s">
-        <v>256</v>
+      <c r="AA501" s="11">
+        <v>60</v>
       </c>
       <c r="AB501" s="1">
         <v>18</v>
@@ -55643,7 +55418,7 @@
     </row>
     <row r="502" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A502" s="1" t="s">
-        <v>368</v>
+        <v>292</v>
       </c>
       <c r="B502" s="1" t="s">
         <v>32</v>
@@ -55833,7 +55608,7 @@
     </row>
     <row r="504" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A504" s="1" t="s">
-        <v>419</v>
+        <v>343</v>
       </c>
       <c r="B504" s="1" t="s">
         <v>32</v>
@@ -55928,7 +55703,7 @@
     </row>
     <row r="505" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A505" s="1" t="s">
-        <v>449</v>
+        <v>373</v>
       </c>
       <c r="B505" s="1" t="s">
         <v>32</v>
@@ -56024,7 +55799,7 @@
     </row>
     <row r="506" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A506" s="1" t="s">
-        <v>454</v>
+        <v>378</v>
       </c>
       <c r="B506" s="1" t="s">
         <v>32</v>
@@ -56119,7 +55894,7 @@
     </row>
     <row r="507" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A507" s="1" t="s">
-        <v>308</v>
+        <v>232</v>
       </c>
       <c r="B507" s="1" t="s">
         <v>32</v>
@@ -56216,7 +55991,7 @@
     </row>
     <row r="508" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A508" s="1" t="s">
-        <v>344</v>
+        <v>268</v>
       </c>
       <c r="B508" s="1" t="s">
         <v>32</v>
@@ -56311,7 +56086,7 @@
     </row>
     <row r="509" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A509" s="1" t="s">
-        <v>345</v>
+        <v>269</v>
       </c>
       <c r="B509" s="1" t="s">
         <v>32</v>
@@ -56406,7 +56181,7 @@
     </row>
     <row r="510" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A510" s="1" t="s">
-        <v>303</v>
+        <v>227</v>
       </c>
       <c r="B510" s="1" t="s">
         <v>32</v>
@@ -56503,7 +56278,7 @@
     </row>
     <row r="511" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A511" s="1" t="s">
-        <v>387</v>
+        <v>311</v>
       </c>
       <c r="B511" s="1" t="s">
         <v>32</v>
@@ -56598,7 +56373,7 @@
     </row>
     <row r="512" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A512" s="1" t="s">
-        <v>556</v>
+        <v>480</v>
       </c>
       <c r="B512" s="1" t="s">
         <v>32</v>
@@ -56694,7 +56469,7 @@
     </row>
     <row r="513" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A513" s="4" t="s">
-        <v>483</v>
+        <v>407</v>
       </c>
       <c r="B513" s="1" t="s">
         <v>32</v>
@@ -56790,7 +56565,7 @@
     </row>
     <row r="514" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A514" s="4" t="s">
-        <v>657</v>
+        <v>581</v>
       </c>
       <c r="B514" s="1" t="s">
         <v>32</v>
@@ -56886,7 +56661,7 @@
     </row>
     <row r="515" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A515" s="4" t="s">
-        <v>490</v>
+        <v>414</v>
       </c>
       <c r="B515" s="1" t="s">
         <v>32</v>
@@ -56982,7 +56757,7 @@
     </row>
     <row r="516" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A516" s="4" t="s">
-        <v>661</v>
+        <v>585</v>
       </c>
       <c r="B516" s="1" t="s">
         <v>32</v>
@@ -57269,7 +57044,7 @@
     </row>
     <row r="519" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A519" s="4" t="s">
-        <v>629</v>
+        <v>553</v>
       </c>
       <c r="B519" s="1" t="s">
         <v>32</v>
@@ -57365,7 +57140,7 @@
     </row>
     <row r="520" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A520" s="1" t="s">
-        <v>414</v>
+        <v>338</v>
       </c>
       <c r="B520" s="1" t="s">
         <v>32</v>
@@ -57460,7 +57235,7 @@
     </row>
     <row r="521" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A521" s="1" t="s">
-        <v>418</v>
+        <v>342</v>
       </c>
       <c r="B521" s="1" t="s">
         <v>32</v>
@@ -57555,7 +57330,7 @@
     </row>
     <row r="522" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A522" s="1" t="s">
-        <v>539</v>
+        <v>463</v>
       </c>
       <c r="B522" s="1" t="s">
         <v>32</v>
@@ -57650,7 +57425,7 @@
     </row>
     <row r="523" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A523" s="1" t="s">
-        <v>537</v>
+        <v>461</v>
       </c>
       <c r="B523" s="1" t="s">
         <v>32</v>
@@ -57745,7 +57520,7 @@
     </row>
     <row r="524" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A524" s="1" t="s">
-        <v>442</v>
+        <v>366</v>
       </c>
       <c r="B524" s="1" t="s">
         <v>32</v>
@@ -57840,7 +57615,7 @@
     </row>
     <row r="525" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A525" s="1" t="s">
-        <v>326</v>
+        <v>250</v>
       </c>
       <c r="B525" s="1" t="s">
         <v>32</v>
@@ -57935,7 +57710,7 @@
     </row>
     <row r="526" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A526" s="1" t="s">
-        <v>455</v>
+        <v>379</v>
       </c>
       <c r="B526" s="1" t="s">
         <v>32</v>
@@ -58031,7 +57806,7 @@
     </row>
     <row r="527" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A527" s="1" t="s">
-        <v>287</v>
+        <v>212</v>
       </c>
       <c r="B527" s="1" t="s">
         <v>32</v>
@@ -58039,8 +57814,8 @@
       <c r="C527" s="1">
         <v>1</v>
       </c>
-      <c r="D527" s="1" t="s">
-        <v>288</v>
+      <c r="D527" s="11">
+        <v>1398</v>
       </c>
       <c r="E527" s="5">
         <v>1</v>
@@ -58128,7 +57903,7 @@
     </row>
     <row r="528" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A528" s="1" t="s">
-        <v>445</v>
+        <v>369</v>
       </c>
       <c r="B528" s="1" t="s">
         <v>32</v>
@@ -58223,7 +57998,7 @@
     </row>
     <row r="529" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A529" s="1" t="s">
-        <v>453</v>
+        <v>377</v>
       </c>
       <c r="B529" s="1" t="s">
         <v>32</v>
@@ -58319,7 +58094,7 @@
     </row>
     <row r="530" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A530" s="1" t="s">
-        <v>669</v>
+        <v>593</v>
       </c>
       <c r="B530" s="1" t="s">
         <v>32</v>
@@ -58415,7 +58190,7 @@
     </row>
     <row r="531" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A531" s="1" t="s">
-        <v>538</v>
+        <v>462</v>
       </c>
       <c r="B531" s="1" t="s">
         <v>32</v>
@@ -58510,7 +58285,7 @@
     </row>
     <row r="532" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A532" s="1" t="s">
-        <v>541</v>
+        <v>465</v>
       </c>
       <c r="B532" s="1" t="s">
         <v>32</v>
@@ -58605,7 +58380,7 @@
     </row>
     <row r="533" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A533" s="1" t="s">
-        <v>295</v>
+        <v>219</v>
       </c>
       <c r="B533" s="1" t="s">
         <v>32</v>
@@ -58702,7 +58477,7 @@
     </row>
     <row r="534" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A534" s="1" t="s">
-        <v>334</v>
+        <v>258</v>
       </c>
       <c r="B534" s="1" t="s">
         <v>32</v>
@@ -58797,7 +58572,7 @@
     </row>
     <row r="535" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A535" s="1" t="s">
-        <v>540</v>
+        <v>464</v>
       </c>
       <c r="B535" s="1" t="s">
         <v>32</v>
@@ -58892,7 +58667,7 @@
     </row>
     <row r="536" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A536" s="1" t="s">
-        <v>586</v>
+        <v>510</v>
       </c>
       <c r="B536" s="1" t="s">
         <v>76</v>
@@ -59178,7 +58953,7 @@
     </row>
     <row r="539" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A539" s="4" t="s">
-        <v>602</v>
+        <v>526</v>
       </c>
       <c r="B539" s="1" t="s">
         <v>32</v>
@@ -59274,7 +59049,7 @@
     </row>
     <row r="540" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A540" s="1" t="s">
-        <v>568</v>
+        <v>492</v>
       </c>
       <c r="B540" s="1" t="s">
         <v>32</v>
@@ -59369,7 +59144,7 @@
     </row>
     <row r="541" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A541" s="1" t="s">
-        <v>503</v>
+        <v>427</v>
       </c>
       <c r="B541" s="1" t="s">
         <v>32</v>
@@ -59468,7 +59243,7 @@
     </row>
     <row r="542" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A542" s="1" t="s">
-        <v>352</v>
+        <v>276</v>
       </c>
       <c r="B542" s="1" t="s">
         <v>32</v>
@@ -59658,7 +59433,7 @@
     </row>
     <row r="544" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A544" s="1" t="s">
-        <v>405</v>
+        <v>329</v>
       </c>
       <c r="B544" s="1" t="s">
         <v>32</v>
@@ -59849,7 +59624,7 @@
     </row>
     <row r="546" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A546" s="4" t="s">
-        <v>636</v>
+        <v>560</v>
       </c>
       <c r="B546" s="1" t="s">
         <v>32</v>
@@ -59945,7 +59720,7 @@
     </row>
     <row r="547" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A547" s="1" t="s">
-        <v>429</v>
+        <v>353</v>
       </c>
       <c r="B547" s="1" t="s">
         <v>32</v>
@@ -60135,7 +59910,7 @@
     </row>
     <row r="549" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A549" s="1" t="s">
-        <v>491</v>
+        <v>415</v>
       </c>
       <c r="B549" s="1" t="s">
         <v>32</v>
@@ -60230,7 +60005,7 @@
     </row>
     <row r="550" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A550" s="1" t="s">
-        <v>332</v>
+        <v>256</v>
       </c>
       <c r="B550" s="1" t="s">
         <v>32</v>
@@ -60325,7 +60100,7 @@
     </row>
     <row r="551" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A551" s="1" t="s">
-        <v>347</v>
+        <v>271</v>
       </c>
       <c r="B551" s="1" t="s">
         <v>32</v>
@@ -60420,7 +60195,7 @@
     </row>
     <row r="552" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A552" s="1" t="s">
-        <v>364</v>
+        <v>288</v>
       </c>
       <c r="B552" s="1" t="s">
         <v>32</v>
@@ -60515,7 +60290,7 @@
     </row>
     <row r="553" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A553" s="1" t="s">
-        <v>546</v>
+        <v>470</v>
       </c>
       <c r="B553" s="1" t="s">
         <v>32</v>
@@ -60610,7 +60385,7 @@
     </row>
     <row r="554" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A554" s="1" t="s">
-        <v>492</v>
+        <v>416</v>
       </c>
       <c r="B554" s="1" t="s">
         <v>32</v>
@@ -60704,12 +60479,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AF554" xr:uid="{00000000-0001-0000-0800-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AF554">
-      <sortCondition ref="A1:A554"/>
-    </sortState>
-  </autoFilter>
-  <conditionalFormatting sqref="A75:AF79 A81:AF98 A80:AB80 AD80:AF80 A100:AF110 A99:AB99 AD99:AF99 A112:AF117 A111:AB111 AD111:AF111 A119:AF123 A118:AB118 AD118:AF118 A126:AF133 A124:AB125 AD124:AF125 A135:AF160 A134:AB134 AD134:AF134 A162:AF164 A161:AB161 AD161:AF161 A166:AF166 A165:AB165 AD165:AF165 A168:AF171 A167:AB167 AD167:AF167 A173:AF210 A172:AB172 AD172:AF172">
+  <conditionalFormatting sqref="A75:AF79 A81:AF98 A100:AF110 A112:AF117 A119:AF123 A126:AF133 A135:AF160 A162:AF164 A166:AF166 A168:AF171 A173:AF210 A80:AB80 AD80:AF80 A99:AB99 AD99:AF99 A111:AB111 AD111:AF111 A118:AB118 AD118:AF118 A124:AB125 AD124:AF125 A134:AB134 AD134:AF134 A161:AB161 AD161:AF161 A165:AB165 AD165:AF165 A167:AB167 AD167:AF167 A172:AB172 AD172:AF172">
     <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>"x"</formula>
     </cfRule>
